--- a/data/demog/Jones/jp_size.xlsx
+++ b/data/demog/Jones/jp_size.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/lipo6619_colorado_edu/Documents/Desktop/Dissertation/natural_demog/data/demog/Jones/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{FE0771E2-720B-A34D-8642-658C8409FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A89E934-7ABD-7242-B47A-E260886250D8}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{FE0771E2-720B-A34D-8642-658C8409FA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CECCAA05-172A-F24D-AFDD-458FE193168D}"/>
   <bookViews>
-    <workbookView xWindow="46960" yWindow="-10860" windowWidth="34640" windowHeight="25180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1020" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jp2023demog_readyforDataEntry" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">jp2023demog_readyforDataEntry!$P$1:$P$887</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">jp2023demog_readyforDataEntry!$C$1:$C$887</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">jp2023demog_readyforDataEntry!$A:$S</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">jp2023demog_readyforDataEntry!$1:$1</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="229">
   <si>
     <t>plot</t>
   </si>
@@ -1372,10 +1372,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -1673,6 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S887"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="11" customHeight="1"/>
   <cols>
@@ -1748,7 +1745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="11" customHeight="1">
+    <row r="2" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>19</v>
       </c>
@@ -1805,7 +1802,7 @@
       </c>
       <c r="S2" s="10"/>
     </row>
-    <row r="3" spans="1:19" ht="11" customHeight="1">
+    <row r="3" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>19</v>
       </c>
@@ -1862,7 +1859,7 @@
       </c>
       <c r="S3" s="10"/>
     </row>
-    <row r="4" spans="1:19" ht="11" customHeight="1">
+    <row r="4" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -1915,7 +1912,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="11" customHeight="1">
+    <row r="5" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1974,7 +1971,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="11" customHeight="1">
+    <row r="6" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>19</v>
       </c>
@@ -2033,7 +2030,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="11" customHeight="1">
+    <row r="7" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>19</v>
       </c>
@@ -2090,7 +2087,7 @@
       </c>
       <c r="S7" s="10"/>
     </row>
-    <row r="8" spans="1:19" ht="11" customHeight="1">
+    <row r="8" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
@@ -2143,7 +2140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="11" customHeight="1">
+    <row r="9" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>19</v>
       </c>
@@ -2202,7 +2199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="11" customHeight="1">
+    <row r="10" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2261,7 +2258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="11" customHeight="1">
+    <row r="11" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>19</v>
       </c>
@@ -2314,7 +2311,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="11" customHeight="1">
+    <row r="12" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -2373,7 +2370,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="11" customHeight="1">
+    <row r="13" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>19</v>
       </c>
@@ -2432,7 +2429,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="11" customHeight="1">
+    <row r="14" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>19</v>
       </c>
@@ -2485,7 +2482,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="11" customHeight="1">
+    <row r="15" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
@@ -2542,7 +2539,7 @@
       </c>
       <c r="S15" s="10"/>
     </row>
-    <row r="16" spans="1:19" ht="11" customHeight="1">
+    <row r="16" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>19</v>
       </c>
@@ -2599,7 +2596,7 @@
       </c>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="1:19" ht="11" customHeight="1">
+    <row r="17" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>19</v>
       </c>
@@ -2656,7 +2653,7 @@
       </c>
       <c r="S17" s="10"/>
     </row>
-    <row r="18" spans="1:19" ht="11" customHeight="1">
+    <row r="18" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>19</v>
       </c>
@@ -2713,7 +2710,7 @@
       </c>
       <c r="S18" s="10"/>
     </row>
-    <row r="19" spans="1:19" ht="11" customHeight="1">
+    <row r="19" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>19</v>
       </c>
@@ -2766,7 +2763,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="11" customHeight="1">
+    <row r="20" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>19</v>
       </c>
@@ -2819,7 +2816,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="11" customHeight="1">
+    <row r="21" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>19</v>
       </c>
@@ -2876,7 +2873,7 @@
       </c>
       <c r="S21" s="10"/>
     </row>
-    <row r="22" spans="1:19" ht="11" customHeight="1">
+    <row r="22" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>19</v>
       </c>
@@ -2929,7 +2926,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="11" customHeight="1">
+    <row r="23" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>19</v>
       </c>
@@ -2988,7 +2985,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="11" customHeight="1">
+    <row r="24" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3045,7 +3042,7 @@
       </c>
       <c r="S24" s="10"/>
     </row>
-    <row r="25" spans="1:19" ht="11" customHeight="1">
+    <row r="25" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>19</v>
       </c>
@@ -3102,7 +3099,7 @@
       </c>
       <c r="S25" s="10"/>
     </row>
-    <row r="26" spans="1:19" ht="11" customHeight="1">
+    <row r="26" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>19</v>
       </c>
@@ -3161,7 +3158,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="11" customHeight="1">
+    <row r="27" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>19</v>
       </c>
@@ -3218,7 +3215,7 @@
       </c>
       <c r="S27" s="10"/>
     </row>
-    <row r="28" spans="1:19" ht="11" customHeight="1">
+    <row r="28" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>19</v>
       </c>
@@ -3277,7 +3274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="11" customHeight="1">
+    <row r="29" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>19</v>
       </c>
@@ -3334,7 +3331,7 @@
       </c>
       <c r="S29" s="10"/>
     </row>
-    <row r="30" spans="1:19" ht="11" customHeight="1">
+    <row r="30" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>19</v>
       </c>
@@ -3393,7 +3390,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="11" customHeight="1">
+    <row r="31" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3450,7 +3447,7 @@
       </c>
       <c r="S31" s="10"/>
     </row>
-    <row r="32" spans="1:19" ht="11" customHeight="1">
+    <row r="32" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>19</v>
       </c>
@@ -3509,7 +3506,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="11" customHeight="1">
+    <row r="33" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>19</v>
       </c>
@@ -3562,7 +3559,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="11" customHeight="1">
+    <row r="34" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>19</v>
       </c>
@@ -3621,7 +3618,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="11" customHeight="1">
+    <row r="35" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>19</v>
       </c>
@@ -3678,7 +3675,7 @@
       </c>
       <c r="S35" s="10"/>
     </row>
-    <row r="36" spans="1:19" ht="11" customHeight="1">
+    <row r="36" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>19</v>
       </c>
@@ -3735,7 +3732,7 @@
       </c>
       <c r="S36" s="10"/>
     </row>
-    <row r="37" spans="1:19" ht="11" customHeight="1">
+    <row r="37" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>19</v>
       </c>
@@ -3794,7 +3791,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="11" customHeight="1">
+    <row r="38" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>19</v>
       </c>
@@ -3851,7 +3848,7 @@
       </c>
       <c r="S38" s="10"/>
     </row>
-    <row r="39" spans="1:19" ht="11" customHeight="1">
+    <row r="39" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>19</v>
       </c>
@@ -3908,7 +3905,7 @@
       </c>
       <c r="S39" s="10"/>
     </row>
-    <row r="40" spans="1:19" ht="11" customHeight="1">
+    <row r="40" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>19</v>
       </c>
@@ -3965,7 +3962,7 @@
       </c>
       <c r="S40" s="10"/>
     </row>
-    <row r="41" spans="1:19" ht="11" customHeight="1">
+    <row r="41" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>19</v>
       </c>
@@ -4022,7 +4019,7 @@
       </c>
       <c r="S41" s="10"/>
     </row>
-    <row r="42" spans="1:19" ht="11" customHeight="1">
+    <row r="42" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>19</v>
       </c>
@@ -4079,7 +4076,7 @@
       </c>
       <c r="S42" s="10"/>
     </row>
-    <row r="43" spans="1:19" ht="11" customHeight="1">
+    <row r="43" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>19</v>
       </c>
@@ -4136,7 +4133,7 @@
       </c>
       <c r="S43" s="10"/>
     </row>
-    <row r="44" spans="1:19" ht="11" customHeight="1">
+    <row r="44" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>19</v>
       </c>
@@ -4195,7 +4192,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="11" customHeight="1">
+    <row r="45" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4254,7 +4251,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="11" customHeight="1">
+    <row r="46" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>19</v>
       </c>
@@ -4311,7 +4308,7 @@
       </c>
       <c r="S46" s="10"/>
     </row>
-    <row r="47" spans="1:19" ht="11" customHeight="1">
+    <row r="47" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>19</v>
       </c>
@@ -4364,7 +4361,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="11" customHeight="1">
+    <row r="48" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>19</v>
       </c>
@@ -4417,7 +4414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="11" customHeight="1">
+    <row r="49" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>19</v>
       </c>
@@ -4474,7 +4471,7 @@
       </c>
       <c r="S49" s="10"/>
     </row>
-    <row r="50" spans="1:19" ht="11" customHeight="1">
+    <row r="50" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>19</v>
       </c>
@@ -4533,7 +4530,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="11" customHeight="1">
+    <row r="51" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>19</v>
       </c>
@@ -4590,7 +4587,7 @@
       </c>
       <c r="S51" s="10"/>
     </row>
-    <row r="52" spans="1:19" ht="11" customHeight="1">
+    <row r="52" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4647,7 +4644,7 @@
       </c>
       <c r="S52" s="10"/>
     </row>
-    <row r="53" spans="1:19" ht="11" customHeight="1">
+    <row r="53" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>19</v>
       </c>
@@ -4704,7 +4701,7 @@
       </c>
       <c r="S53" s="10"/>
     </row>
-    <row r="54" spans="1:19" ht="11" customHeight="1">
+    <row r="54" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>19</v>
       </c>
@@ -4761,7 +4758,7 @@
       </c>
       <c r="S54" s="10"/>
     </row>
-    <row r="55" spans="1:19" ht="11" customHeight="1">
+    <row r="55" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>19</v>
       </c>
@@ -4820,7 +4817,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="11" customHeight="1">
+    <row r="56" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>19</v>
       </c>
@@ -4877,7 +4874,7 @@
       </c>
       <c r="S56" s="10"/>
     </row>
-    <row r="57" spans="1:19" ht="11" customHeight="1">
+    <row r="57" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>19</v>
       </c>
@@ -4934,7 +4931,7 @@
       </c>
       <c r="S57" s="10"/>
     </row>
-    <row r="58" spans="1:19" ht="11" customHeight="1">
+    <row r="58" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>19</v>
       </c>
@@ -4991,7 +4988,7 @@
       </c>
       <c r="S58" s="10"/>
     </row>
-    <row r="59" spans="1:19" ht="11" customHeight="1">
+    <row r="59" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5048,7 +5045,7 @@
       </c>
       <c r="S59" s="10"/>
     </row>
-    <row r="60" spans="1:19" ht="11" customHeight="1">
+    <row r="60" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>19</v>
       </c>
@@ -5105,7 +5102,7 @@
       </c>
       <c r="S60" s="10"/>
     </row>
-    <row r="61" spans="1:19" ht="11" customHeight="1">
+    <row r="61" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A61" s="8" t="s">
         <v>19</v>
       </c>
@@ -5162,7 +5159,7 @@
       </c>
       <c r="S61" s="10"/>
     </row>
-    <row r="62" spans="1:19" ht="11" customHeight="1">
+    <row r="62" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A62" s="8" t="s">
         <v>19</v>
       </c>
@@ -5221,7 +5218,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="11" customHeight="1">
+    <row r="63" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A63" s="8" t="s">
         <v>19</v>
       </c>
@@ -5274,7 +5271,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="11" customHeight="1">
+    <row r="64" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>19</v>
       </c>
@@ -5331,7 +5328,7 @@
       </c>
       <c r="S64" s="10"/>
     </row>
-    <row r="65" spans="1:19" ht="11" customHeight="1">
+    <row r="65" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A65" s="8" t="s">
         <v>19</v>
       </c>
@@ -5388,7 +5385,7 @@
       </c>
       <c r="S65" s="10"/>
     </row>
-    <row r="66" spans="1:19" ht="11" customHeight="1">
+    <row r="66" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>19</v>
       </c>
@@ -5447,7 +5444,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="11" customHeight="1">
+    <row r="67" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>19</v>
       </c>
@@ -5500,7 +5497,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="11" customHeight="1">
+    <row r="68" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>19</v>
       </c>
@@ -5557,7 +5554,7 @@
       </c>
       <c r="S68" s="10"/>
     </row>
-    <row r="69" spans="1:19" ht="11" customHeight="1">
+    <row r="69" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>19</v>
       </c>
@@ -5610,7 +5607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="11" customHeight="1">
+    <row r="70" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>19</v>
       </c>
@@ -5667,7 +5664,7 @@
       </c>
       <c r="S70" s="10"/>
     </row>
-    <row r="71" spans="1:19" ht="11" customHeight="1">
+    <row r="71" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>19</v>
       </c>
@@ -5726,7 +5723,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="11" customHeight="1">
+    <row r="72" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>19</v>
       </c>
@@ -5785,7 +5782,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="11" customHeight="1">
+    <row r="73" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>19</v>
       </c>
@@ -5832,7 +5829,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="11" customHeight="1">
+    <row r="74" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>19</v>
       </c>
@@ -5889,7 +5886,7 @@
       </c>
       <c r="S74" s="10"/>
     </row>
-    <row r="75" spans="1:19" ht="11" customHeight="1">
+    <row r="75" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>19</v>
       </c>
@@ -5946,7 +5943,7 @@
       </c>
       <c r="S75" s="10"/>
     </row>
-    <row r="76" spans="1:19" ht="11" customHeight="1">
+    <row r="76" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>19</v>
       </c>
@@ -6003,7 +6000,7 @@
       </c>
       <c r="S76" s="10"/>
     </row>
-    <row r="77" spans="1:19" ht="11" customHeight="1">
+    <row r="77" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>19</v>
       </c>
@@ -6060,7 +6057,7 @@
       </c>
       <c r="S77" s="10"/>
     </row>
-    <row r="78" spans="1:19" ht="11" customHeight="1">
+    <row r="78" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>19</v>
       </c>
@@ -6117,7 +6114,7 @@
       </c>
       <c r="S78" s="10"/>
     </row>
-    <row r="79" spans="1:19" ht="11" customHeight="1">
+    <row r="79" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A79" s="8" t="s">
         <v>19</v>
       </c>
@@ -6176,7 +6173,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="11" customHeight="1">
+    <row r="80" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A80" s="8" t="s">
         <v>19</v>
       </c>
@@ -6235,7 +6232,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="11" customHeight="1">
+    <row r="81" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A81" s="8" t="s">
         <v>19</v>
       </c>
@@ -6294,7 +6291,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="11" customHeight="1">
+    <row r="82" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A82" s="8" t="s">
         <v>19</v>
       </c>
@@ -6351,7 +6348,7 @@
       </c>
       <c r="S82" s="10"/>
     </row>
-    <row r="83" spans="1:19" ht="11" customHeight="1">
+    <row r="83" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A83" s="8" t="s">
         <v>19</v>
       </c>
@@ -6410,7 +6407,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="11" customHeight="1">
+    <row r="84" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>19</v>
       </c>
@@ -6467,7 +6464,7 @@
       </c>
       <c r="S84" s="10"/>
     </row>
-    <row r="85" spans="1:19" ht="11" customHeight="1">
+    <row r="85" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A85" s="8" t="s">
         <v>19</v>
       </c>
@@ -6524,7 +6521,7 @@
       </c>
       <c r="S85" s="10"/>
     </row>
-    <row r="86" spans="1:19" ht="11" customHeight="1">
+    <row r="86" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A86" s="8" t="s">
         <v>19</v>
       </c>
@@ -6581,7 +6578,7 @@
       </c>
       <c r="S86" s="10"/>
     </row>
-    <row r="87" spans="1:19" ht="11" customHeight="1">
+    <row r="87" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A87" s="8" t="s">
         <v>19</v>
       </c>
@@ -6640,7 +6637,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="11" customHeight="1">
+    <row r="88" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A88" s="8" t="s">
         <v>19</v>
       </c>
@@ -6693,7 +6690,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="11" customHeight="1">
+    <row r="89" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A89" s="8" t="s">
         <v>19</v>
       </c>
@@ -6750,7 +6747,7 @@
       </c>
       <c r="S89" s="10"/>
     </row>
-    <row r="90" spans="1:19" ht="11" customHeight="1">
+    <row r="90" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A90" s="8" t="s">
         <v>19</v>
       </c>
@@ -6809,7 +6806,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="11" customHeight="1">
+    <row r="91" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A91" s="8" t="s">
         <v>19</v>
       </c>
@@ -6868,7 +6865,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="11" customHeight="1">
+    <row r="92" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A92" s="8" t="s">
         <v>19</v>
       </c>
@@ -6925,7 +6922,7 @@
       </c>
       <c r="S92" s="10"/>
     </row>
-    <row r="93" spans="1:19" ht="11" customHeight="1">
+    <row r="93" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A93" s="8" t="s">
         <v>19</v>
       </c>
@@ -6982,7 +6979,7 @@
       </c>
       <c r="S93" s="10"/>
     </row>
-    <row r="94" spans="1:19" ht="11" customHeight="1">
+    <row r="94" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A94" s="8" t="s">
         <v>19</v>
       </c>
@@ -7039,7 +7036,7 @@
       </c>
       <c r="S94" s="10"/>
     </row>
-    <row r="95" spans="1:19" ht="11" customHeight="1">
+    <row r="95" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A95" s="8" t="s">
         <v>19</v>
       </c>
@@ -7098,7 +7095,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="11" customHeight="1">
+    <row r="96" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A96" s="8" t="s">
         <v>19</v>
       </c>
@@ -7155,7 +7152,7 @@
       </c>
       <c r="S96" s="10"/>
     </row>
-    <row r="97" spans="1:19" ht="11" customHeight="1">
+    <row r="97" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>19</v>
       </c>
@@ -7212,7 +7209,7 @@
       </c>
       <c r="S97" s="10"/>
     </row>
-    <row r="98" spans="1:19" ht="11" customHeight="1">
+    <row r="98" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A98" s="8" t="s">
         <v>19</v>
       </c>
@@ -7271,7 +7268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="11" customHeight="1">
+    <row r="99" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A99" s="8" t="s">
         <v>19</v>
       </c>
@@ -7330,7 +7327,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="11" customHeight="1">
+    <row r="100" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A100" s="8" t="s">
         <v>19</v>
       </c>
@@ -7389,7 +7386,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="11" customHeight="1">
+    <row r="101" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A101" s="8" t="s">
         <v>19</v>
       </c>
@@ -7440,7 +7437,7 @@
       </c>
       <c r="S101" s="10"/>
     </row>
-    <row r="102" spans="1:19" ht="11" customHeight="1">
+    <row r="102" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A102" s="8" t="s">
         <v>19</v>
       </c>
@@ -7491,7 +7488,7 @@
       </c>
       <c r="S102" s="10"/>
     </row>
-    <row r="103" spans="1:19" ht="11" customHeight="1">
+    <row r="103" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A103" s="8" t="s">
         <v>19</v>
       </c>
@@ -7548,7 +7545,7 @@
       </c>
       <c r="S103" s="10"/>
     </row>
-    <row r="104" spans="1:19" ht="11" customHeight="1">
+    <row r="104" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A104" s="8" t="s">
         <v>19</v>
       </c>
@@ -7607,7 +7604,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="11" customHeight="1">
+    <row r="105" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A105" s="8" t="s">
         <v>19</v>
       </c>
@@ -7660,7 +7657,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="11" customHeight="1">
+    <row r="106" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A106" s="8" t="s">
         <v>19</v>
       </c>
@@ -7717,7 +7714,7 @@
       </c>
       <c r="S106" s="10"/>
     </row>
-    <row r="107" spans="1:19" ht="11" customHeight="1">
+    <row r="107" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A107" s="8" t="s">
         <v>19</v>
       </c>
@@ -7776,7 +7773,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="11" customHeight="1">
+    <row r="108" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A108" s="8" t="s">
         <v>19</v>
       </c>
@@ -7833,7 +7830,7 @@
       </c>
       <c r="S108" s="10"/>
     </row>
-    <row r="109" spans="1:19" ht="11" customHeight="1">
+    <row r="109" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A109" s="8" t="s">
         <v>19</v>
       </c>
@@ -7890,7 +7887,7 @@
       </c>
       <c r="S109" s="10"/>
     </row>
-    <row r="110" spans="1:19" ht="11" customHeight="1">
+    <row r="110" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>19</v>
       </c>
@@ -7949,7 +7946,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="11" customHeight="1">
+    <row r="111" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A111" s="8" t="s">
         <v>19</v>
       </c>
@@ -8006,7 +8003,7 @@
       </c>
       <c r="S111" s="10"/>
     </row>
-    <row r="112" spans="1:19" ht="11" customHeight="1">
+    <row r="112" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A112" s="8" t="s">
         <v>19</v>
       </c>
@@ -8065,7 +8062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="11" customHeight="1">
+    <row r="113" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A113" s="8" t="s">
         <v>19</v>
       </c>
@@ -8147,8 +8144,8 @@
       <c r="H114" s="16">
         <v>108</v>
       </c>
-      <c r="I114" s="16" t="s">
-        <v>79</v>
+      <c r="I114" s="16">
+        <v>0</v>
       </c>
       <c r="J114" s="16" t="s">
         <v>80</v>
@@ -8181,7 +8178,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="11" customHeight="1">
+    <row r="115" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A115" s="8" t="s">
         <v>19</v>
       </c>
@@ -8240,7 +8237,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="11" customHeight="1">
+    <row r="116" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A116" s="8" t="s">
         <v>19</v>
       </c>
@@ -8299,7 +8296,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="117" spans="1:19" ht="11" customHeight="1">
+    <row r="117" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A117" s="8" t="s">
         <v>19</v>
       </c>
@@ -8358,7 +8355,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="11" customHeight="1">
+    <row r="118" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A118" s="8" t="s">
         <v>19</v>
       </c>
@@ -8415,7 +8412,7 @@
       </c>
       <c r="S118" s="10"/>
     </row>
-    <row r="119" spans="1:19" ht="11" customHeight="1">
+    <row r="119" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A119" s="8" t="s">
         <v>19</v>
       </c>
@@ -8472,7 +8469,7 @@
       </c>
       <c r="S119" s="10"/>
     </row>
-    <row r="120" spans="1:19" ht="11" customHeight="1">
+    <row r="120" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A120" s="8" t="s">
         <v>19</v>
       </c>
@@ -8531,7 +8528,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="11" customHeight="1">
+    <row r="121" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A121" s="8" t="s">
         <v>19</v>
       </c>
@@ -8588,7 +8585,7 @@
       </c>
       <c r="S121" s="10"/>
     </row>
-    <row r="122" spans="1:19" ht="11" customHeight="1">
+    <row r="122" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A122" s="8" t="s">
         <v>19</v>
       </c>
@@ -8647,7 +8644,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="11" customHeight="1">
+    <row r="123" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A123" s="8" t="s">
         <v>19</v>
       </c>
@@ -8706,7 +8703,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="11" customHeight="1">
+    <row r="124" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A124" s="8" t="s">
         <v>19</v>
       </c>
@@ -8763,7 +8760,7 @@
       </c>
       <c r="S124" s="10"/>
     </row>
-    <row r="125" spans="1:19" ht="11" customHeight="1">
+    <row r="125" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A125" s="8" t="s">
         <v>19</v>
       </c>
@@ -8820,7 +8817,7 @@
       </c>
       <c r="S125" s="10"/>
     </row>
-    <row r="126" spans="1:19" ht="11" customHeight="1">
+    <row r="126" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A126" s="8" t="s">
         <v>19</v>
       </c>
@@ -8877,7 +8874,7 @@
       </c>
       <c r="S126" s="10"/>
     </row>
-    <row r="127" spans="1:19" ht="11" customHeight="1">
+    <row r="127" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A127" s="8" t="s">
         <v>19</v>
       </c>
@@ -8934,7 +8931,7 @@
       </c>
       <c r="S127" s="10"/>
     </row>
-    <row r="128" spans="1:19" ht="11" customHeight="1">
+    <row r="128" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A128" s="8" t="s">
         <v>19</v>
       </c>
@@ -8991,7 +8988,7 @@
       </c>
       <c r="S128" s="10"/>
     </row>
-    <row r="129" spans="1:19" ht="11" customHeight="1">
+    <row r="129" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A129" s="8" t="s">
         <v>19</v>
       </c>
@@ -9048,7 +9045,7 @@
       </c>
       <c r="S129" s="10"/>
     </row>
-    <row r="130" spans="1:19" ht="11" customHeight="1">
+    <row r="130" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A130" s="8" t="s">
         <v>19</v>
       </c>
@@ -9105,7 +9102,7 @@
       </c>
       <c r="S130" s="10"/>
     </row>
-    <row r="131" spans="1:19" ht="11" customHeight="1">
+    <row r="131" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A131" s="8" t="s">
         <v>19</v>
       </c>
@@ -9164,7 +9161,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="11" customHeight="1">
+    <row r="132" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A132" s="8" t="s">
         <v>19</v>
       </c>
@@ -9223,7 +9220,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="11" customHeight="1">
+    <row r="133" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A133" s="8" t="s">
         <v>19</v>
       </c>
@@ -9282,7 +9279,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="11" customHeight="1">
+    <row r="134" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A134" s="8" t="s">
         <v>19</v>
       </c>
@@ -9341,7 +9338,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="135" spans="1:19" ht="11" customHeight="1">
+    <row r="135" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A135" s="8" t="s">
         <v>19</v>
       </c>
@@ -9400,7 +9397,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="11" customHeight="1">
+    <row r="136" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A136" s="8" t="s">
         <v>87</v>
       </c>
@@ -9457,7 +9454,7 @@
       </c>
       <c r="S136" s="10"/>
     </row>
-    <row r="137" spans="1:19" ht="11" customHeight="1">
+    <row r="137" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A137" s="8" t="s">
         <v>87</v>
       </c>
@@ -9514,7 +9511,7 @@
       </c>
       <c r="S137" s="10"/>
     </row>
-    <row r="138" spans="1:19" ht="11" customHeight="1">
+    <row r="138" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A138" s="8" t="s">
         <v>87</v>
       </c>
@@ -9571,7 +9568,7 @@
       </c>
       <c r="S138" s="10"/>
     </row>
-    <row r="139" spans="1:19" ht="11" customHeight="1">
+    <row r="139" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A139" s="8" t="s">
         <v>87</v>
       </c>
@@ -9628,7 +9625,7 @@
       </c>
       <c r="S139" s="10"/>
     </row>
-    <row r="140" spans="1:19" ht="11" customHeight="1">
+    <row r="140" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A140" s="8" t="s">
         <v>87</v>
       </c>
@@ -9687,7 +9684,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="11" customHeight="1">
+    <row r="141" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A141" s="8" t="s">
         <v>87</v>
       </c>
@@ -9744,7 +9741,7 @@
       </c>
       <c r="S141" s="10"/>
     </row>
-    <row r="142" spans="1:19" ht="11" customHeight="1">
+    <row r="142" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A142" s="8" t="s">
         <v>87</v>
       </c>
@@ -9803,7 +9800,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="143" spans="1:19" ht="11" customHeight="1">
+    <row r="143" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A143" s="8" t="s">
         <v>87</v>
       </c>
@@ -9860,7 +9857,7 @@
       </c>
       <c r="S143" s="10"/>
     </row>
-    <row r="144" spans="1:19" ht="11" customHeight="1">
+    <row r="144" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A144" s="8" t="s">
         <v>87</v>
       </c>
@@ -9917,7 +9914,7 @@
       </c>
       <c r="S144" s="10"/>
     </row>
-    <row r="145" spans="1:19" ht="11" customHeight="1">
+    <row r="145" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A145" s="8" t="s">
         <v>87</v>
       </c>
@@ -9974,7 +9971,7 @@
       </c>
       <c r="S145" s="10"/>
     </row>
-    <row r="146" spans="1:19" ht="11" customHeight="1">
+    <row r="146" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A146" s="8" t="s">
         <v>87</v>
       </c>
@@ -10031,7 +10028,7 @@
       </c>
       <c r="S146" s="10"/>
     </row>
-    <row r="147" spans="1:19" ht="11" customHeight="1">
+    <row r="147" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A147" s="8" t="s">
         <v>87</v>
       </c>
@@ -10088,7 +10085,7 @@
       </c>
       <c r="S147" s="10"/>
     </row>
-    <row r="148" spans="1:19" ht="11" customHeight="1">
+    <row r="148" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A148" s="8" t="s">
         <v>87</v>
       </c>
@@ -10141,7 +10138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" spans="1:19" ht="11" customHeight="1">
+    <row r="149" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A149" s="8" t="s">
         <v>87</v>
       </c>
@@ -10200,7 +10197,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="150" spans="1:19" ht="11" customHeight="1">
+    <row r="150" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A150" s="8" t="s">
         <v>87</v>
       </c>
@@ -10253,7 +10250,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:19" ht="11" customHeight="1">
+    <row r="151" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A151" s="8" t="s">
         <v>87</v>
       </c>
@@ -10310,7 +10307,7 @@
       </c>
       <c r="S151" s="10"/>
     </row>
-    <row r="152" spans="1:19" ht="11" customHeight="1">
+    <row r="152" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A152" s="8" t="s">
         <v>87</v>
       </c>
@@ -10367,7 +10364,7 @@
       </c>
       <c r="S152" s="10"/>
     </row>
-    <row r="153" spans="1:19" ht="11" customHeight="1">
+    <row r="153" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A153" s="8" t="s">
         <v>87</v>
       </c>
@@ -10420,7 +10417,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="154" spans="1:19" ht="11" customHeight="1">
+    <row r="154" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A154" s="8" t="s">
         <v>87</v>
       </c>
@@ -10477,7 +10474,7 @@
       </c>
       <c r="S154" s="10"/>
     </row>
-    <row r="155" spans="1:19" ht="11" customHeight="1">
+    <row r="155" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A155" s="8" t="s">
         <v>87</v>
       </c>
@@ -10530,7 +10527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="156" spans="1:19" ht="11" customHeight="1">
+    <row r="156" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A156" s="8" t="s">
         <v>87</v>
       </c>
@@ -10589,7 +10586,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="157" spans="1:19" ht="11" customHeight="1">
+    <row r="157" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A157" s="8" t="s">
         <v>87</v>
       </c>
@@ -10642,7 +10639,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="158" spans="1:19" ht="11" customHeight="1">
+    <row r="158" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A158" s="8" t="s">
         <v>87</v>
       </c>
@@ -10695,7 +10692,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:19" ht="11" customHeight="1">
+    <row r="159" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A159" s="8" t="s">
         <v>87</v>
       </c>
@@ -10752,7 +10749,7 @@
       </c>
       <c r="S159" s="10"/>
     </row>
-    <row r="160" spans="1:19" ht="11" customHeight="1">
+    <row r="160" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A160" s="8" t="s">
         <v>87</v>
       </c>
@@ -10811,7 +10808,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="161" spans="1:19" ht="11" customHeight="1">
+    <row r="161" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A161" s="8" t="s">
         <v>87</v>
       </c>
@@ -10864,7 +10861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="162" spans="1:19" ht="11" customHeight="1">
+    <row r="162" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A162" s="8" t="s">
         <v>87</v>
       </c>
@@ -10921,7 +10918,7 @@
       </c>
       <c r="S162" s="10"/>
     </row>
-    <row r="163" spans="1:19" ht="11" customHeight="1">
+    <row r="163" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A163" s="8" t="s">
         <v>87</v>
       </c>
@@ -10974,7 +10971,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="11" customHeight="1">
+    <row r="164" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A164" s="8" t="s">
         <v>87</v>
       </c>
@@ -11031,7 +11028,7 @@
       </c>
       <c r="S164" s="10"/>
     </row>
-    <row r="165" spans="1:19" ht="11" customHeight="1">
+    <row r="165" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A165" s="8" t="s">
         <v>87</v>
       </c>
@@ -11090,7 +11087,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="11" customHeight="1">
+    <row r="166" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A166" s="8" t="s">
         <v>87</v>
       </c>
@@ -11143,7 +11140,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="167" spans="1:19" ht="11" customHeight="1">
+    <row r="167" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A167" s="8" t="s">
         <v>87</v>
       </c>
@@ -11202,7 +11199,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="11" customHeight="1">
+    <row r="168" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A168" s="8" t="s">
         <v>87</v>
       </c>
@@ -11259,7 +11256,7 @@
       </c>
       <c r="S168" s="10"/>
     </row>
-    <row r="169" spans="1:19" ht="11" customHeight="1">
+    <row r="169" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A169" s="8" t="s">
         <v>87</v>
       </c>
@@ -11318,7 +11315,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="11" customHeight="1">
+    <row r="170" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A170" s="8" t="s">
         <v>87</v>
       </c>
@@ -11375,7 +11372,7 @@
       </c>
       <c r="S170" s="10"/>
     </row>
-    <row r="171" spans="1:19" ht="11" customHeight="1">
+    <row r="171" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A171" s="8" t="s">
         <v>87</v>
       </c>
@@ -11434,7 +11431,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="11" customHeight="1">
+    <row r="172" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A172" s="8" t="s">
         <v>87</v>
       </c>
@@ -11487,7 +11484,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="173" spans="1:19" ht="11" customHeight="1">
+    <row r="173" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A173" s="8" t="s">
         <v>87</v>
       </c>
@@ -11546,7 +11543,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="174" spans="1:19" ht="11" customHeight="1">
+    <row r="174" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A174" s="8" t="s">
         <v>87</v>
       </c>
@@ -11605,7 +11602,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="175" spans="1:19" ht="11" customHeight="1">
+    <row r="175" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A175" s="8" t="s">
         <v>87</v>
       </c>
@@ -11662,7 +11659,7 @@
       </c>
       <c r="S175" s="10"/>
     </row>
-    <row r="176" spans="1:19" ht="11" customHeight="1">
+    <row r="176" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A176" s="8" t="s">
         <v>87</v>
       </c>
@@ -11719,7 +11716,7 @@
       </c>
       <c r="S176" s="10"/>
     </row>
-    <row r="177" spans="1:19" ht="11" customHeight="1">
+    <row r="177" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A177" s="8" t="s">
         <v>87</v>
       </c>
@@ -11778,7 +11775,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="178" spans="1:19" ht="11" customHeight="1">
+    <row r="178" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A178" s="8" t="s">
         <v>87</v>
       </c>
@@ -11837,7 +11834,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="11" customHeight="1">
+    <row r="179" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A179" s="8" t="s">
         <v>87</v>
       </c>
@@ -11896,7 +11893,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="11" customHeight="1">
+    <row r="180" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A180" s="8" t="s">
         <v>87</v>
       </c>
@@ -11955,7 +11952,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="181" spans="1:19" ht="11" customHeight="1">
+    <row r="181" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A181" s="8" t="s">
         <v>87</v>
       </c>
@@ -12012,7 +12009,7 @@
       </c>
       <c r="S181" s="10"/>
     </row>
-    <row r="182" spans="1:19" ht="11" customHeight="1">
+    <row r="182" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A182" s="8" t="s">
         <v>87</v>
       </c>
@@ -12071,7 +12068,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="183" spans="1:19" ht="11" customHeight="1">
+    <row r="183" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A183" s="8" t="s">
         <v>87</v>
       </c>
@@ -12130,7 +12127,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:19" ht="11" customHeight="1">
+    <row r="184" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A184" s="8" t="s">
         <v>87</v>
       </c>
@@ -12183,7 +12180,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:19" ht="11" customHeight="1">
+    <row r="185" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A185" s="8" t="s">
         <v>87</v>
       </c>
@@ -12242,7 +12239,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="186" spans="1:19" ht="11" customHeight="1">
+    <row r="186" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A186" s="8" t="s">
         <v>87</v>
       </c>
@@ -12299,7 +12296,7 @@
       </c>
       <c r="S186" s="10"/>
     </row>
-    <row r="187" spans="1:19" ht="11" customHeight="1">
+    <row r="187" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A187" s="8" t="s">
         <v>87</v>
       </c>
@@ -12356,7 +12353,7 @@
       </c>
       <c r="S187" s="10"/>
     </row>
-    <row r="188" spans="1:19" ht="11" customHeight="1">
+    <row r="188" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A188" s="8" t="s">
         <v>87</v>
       </c>
@@ -12409,7 +12406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:19" ht="11" customHeight="1">
+    <row r="189" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A189" s="8" t="s">
         <v>87</v>
       </c>
@@ -12466,7 +12463,7 @@
       </c>
       <c r="S189" s="10"/>
     </row>
-    <row r="190" spans="1:19" ht="11" customHeight="1">
+    <row r="190" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A190" s="8" t="s">
         <v>87</v>
       </c>
@@ -12523,7 +12520,7 @@
       </c>
       <c r="S190" s="10"/>
     </row>
-    <row r="191" spans="1:19" ht="11" customHeight="1">
+    <row r="191" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A191" s="8" t="s">
         <v>87</v>
       </c>
@@ -12576,7 +12573,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="11" customHeight="1">
+    <row r="192" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A192" s="8" t="s">
         <v>87</v>
       </c>
@@ -12635,7 +12632,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="193" spans="1:19" ht="11" customHeight="1">
+    <row r="193" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A193" s="8" t="s">
         <v>87</v>
       </c>
@@ -12694,7 +12691,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="194" spans="1:19" ht="11" customHeight="1">
+    <row r="194" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A194" s="8" t="s">
         <v>87</v>
       </c>
@@ -12747,7 +12744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="195" spans="1:19" ht="11" customHeight="1">
+    <row r="195" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A195" s="8" t="s">
         <v>87</v>
       </c>
@@ -12804,7 +12801,7 @@
       </c>
       <c r="S195" s="10"/>
     </row>
-    <row r="196" spans="1:19" ht="11" customHeight="1">
+    <row r="196" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A196" s="8" t="s">
         <v>87</v>
       </c>
@@ -12861,7 +12858,7 @@
       </c>
       <c r="S196" s="10"/>
     </row>
-    <row r="197" spans="1:19" ht="11" customHeight="1">
+    <row r="197" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A197" s="8" t="s">
         <v>87</v>
       </c>
@@ -12920,7 +12917,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="198" spans="1:19" ht="11" customHeight="1">
+    <row r="198" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A198" s="8" t="s">
         <v>87</v>
       </c>
@@ -12977,7 +12974,7 @@
       </c>
       <c r="S198" s="10"/>
     </row>
-    <row r="199" spans="1:19" ht="11" customHeight="1">
+    <row r="199" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A199" s="8" t="s">
         <v>87</v>
       </c>
@@ -13030,7 +13027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="200" spans="1:19" ht="11" customHeight="1">
+    <row r="200" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A200" s="8" t="s">
         <v>87</v>
       </c>
@@ -13087,7 +13084,7 @@
       </c>
       <c r="S200" s="10"/>
     </row>
-    <row r="201" spans="1:19" ht="11" customHeight="1">
+    <row r="201" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A201" s="8" t="s">
         <v>87</v>
       </c>
@@ -13144,7 +13141,7 @@
       </c>
       <c r="S201" s="10"/>
     </row>
-    <row r="202" spans="1:19" ht="11" customHeight="1">
+    <row r="202" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A202" s="8" t="s">
         <v>87</v>
       </c>
@@ -13201,7 +13198,7 @@
       </c>
       <c r="S202" s="10"/>
     </row>
-    <row r="203" spans="1:19" ht="11" customHeight="1">
+    <row r="203" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A203" s="8" t="s">
         <v>87</v>
       </c>
@@ -13258,7 +13255,7 @@
       </c>
       <c r="S203" s="10"/>
     </row>
-    <row r="204" spans="1:19" ht="11" customHeight="1">
+    <row r="204" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A204" s="8" t="s">
         <v>87</v>
       </c>
@@ -13315,7 +13312,7 @@
       </c>
       <c r="S204" s="10"/>
     </row>
-    <row r="205" spans="1:19" ht="11" customHeight="1">
+    <row r="205" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A205" s="8" t="s">
         <v>87</v>
       </c>
@@ -13374,7 +13371,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="206" spans="1:19" ht="11" customHeight="1">
+    <row r="206" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A206" s="8" t="s">
         <v>87</v>
       </c>
@@ -13433,7 +13430,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="11" customHeight="1">
+    <row r="207" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A207" s="8" t="s">
         <v>87</v>
       </c>
@@ -13492,7 +13489,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="208" spans="1:19" ht="11" customHeight="1">
+    <row r="208" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A208" s="8" t="s">
         <v>87</v>
       </c>
@@ -13549,7 +13546,7 @@
       </c>
       <c r="S208" s="10"/>
     </row>
-    <row r="209" spans="1:19" ht="11" customHeight="1">
+    <row r="209" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A209" s="8" t="s">
         <v>87</v>
       </c>
@@ -13602,7 +13599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="1:19" ht="11" customHeight="1">
+    <row r="210" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A210" s="8" t="s">
         <v>87</v>
       </c>
@@ -13661,7 +13658,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="211" spans="1:19" ht="12" customHeight="1">
+    <row r="211" spans="1:19" ht="12" hidden="1" customHeight="1">
       <c r="A211" s="8" t="s">
         <v>87</v>
       </c>
@@ -13718,7 +13715,7 @@
       </c>
       <c r="S211" s="10"/>
     </row>
-    <row r="212" spans="1:19" ht="11" customHeight="1">
+    <row r="212" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A212" s="8" t="s">
         <v>87</v>
       </c>
@@ -13775,7 +13772,7 @@
       </c>
       <c r="S212" s="10"/>
     </row>
-    <row r="213" spans="1:19" ht="11" customHeight="1">
+    <row r="213" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A213" s="8" t="s">
         <v>87</v>
       </c>
@@ -13832,7 +13829,7 @@
       </c>
       <c r="S213" s="10"/>
     </row>
-    <row r="214" spans="1:19" ht="11" customHeight="1">
+    <row r="214" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A214" s="8" t="s">
         <v>87</v>
       </c>
@@ -13889,7 +13886,7 @@
       </c>
       <c r="S214" s="10"/>
     </row>
-    <row r="215" spans="1:19" ht="11" customHeight="1">
+    <row r="215" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A215" s="8" t="s">
         <v>87</v>
       </c>
@@ -13946,7 +13943,7 @@
       </c>
       <c r="S215" s="10"/>
     </row>
-    <row r="216" spans="1:19" ht="11" customHeight="1">
+    <row r="216" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A216" s="8" t="s">
         <v>87</v>
       </c>
@@ -13999,7 +13996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="217" spans="1:19" ht="11" customHeight="1">
+    <row r="217" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A217" s="8" t="s">
         <v>87</v>
       </c>
@@ -14058,7 +14055,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="218" spans="1:19" ht="11" customHeight="1">
+    <row r="218" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A218" s="8" t="s">
         <v>87</v>
       </c>
@@ -14117,7 +14114,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="219" spans="1:19" ht="11" customHeight="1">
+    <row r="219" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A219" s="8" t="s">
         <v>87</v>
       </c>
@@ -14174,7 +14171,7 @@
       </c>
       <c r="S219" s="10"/>
     </row>
-    <row r="220" spans="1:19" ht="11" customHeight="1">
+    <row r="220" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A220" s="8" t="s">
         <v>87</v>
       </c>
@@ -14231,7 +14228,7 @@
       </c>
       <c r="S220" s="10"/>
     </row>
-    <row r="221" spans="1:19" ht="11" customHeight="1">
+    <row r="221" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A221" s="8" t="s">
         <v>87</v>
       </c>
@@ -14288,7 +14285,7 @@
       </c>
       <c r="S221" s="10"/>
     </row>
-    <row r="222" spans="1:19" ht="11" customHeight="1">
+    <row r="222" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A222" s="8" t="s">
         <v>87</v>
       </c>
@@ -14347,7 +14344,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="11" customHeight="1">
+    <row r="223" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A223" s="8" t="s">
         <v>87</v>
       </c>
@@ -14404,7 +14401,7 @@
       </c>
       <c r="S223" s="10"/>
     </row>
-    <row r="224" spans="1:19" ht="11" customHeight="1">
+    <row r="224" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A224" s="8" t="s">
         <v>87</v>
       </c>
@@ -14461,7 +14458,7 @@
       </c>
       <c r="S224" s="10"/>
     </row>
-    <row r="225" spans="1:19" ht="11" customHeight="1">
+    <row r="225" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A225" s="8" t="s">
         <v>87</v>
       </c>
@@ -14518,7 +14515,7 @@
       </c>
       <c r="S225" s="10"/>
     </row>
-    <row r="226" spans="1:19" ht="11" customHeight="1">
+    <row r="226" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A226" s="8" t="s">
         <v>87</v>
       </c>
@@ -14575,7 +14572,7 @@
       </c>
       <c r="S226" s="10"/>
     </row>
-    <row r="227" spans="1:19" ht="11" customHeight="1">
+    <row r="227" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A227" s="8" t="s">
         <v>87</v>
       </c>
@@ -14634,7 +14631,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="228" spans="1:19" ht="11" customHeight="1">
+    <row r="228" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A228" s="8" t="s">
         <v>87</v>
       </c>
@@ -14687,7 +14684,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="229" spans="1:19" ht="11" customHeight="1">
+    <row r="229" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A229" s="8" t="s">
         <v>87</v>
       </c>
@@ -14744,7 +14741,7 @@
       </c>
       <c r="S229" s="10"/>
     </row>
-    <row r="230" spans="1:19" ht="11" customHeight="1">
+    <row r="230" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A230" s="8" t="s">
         <v>87</v>
       </c>
@@ -14801,7 +14798,7 @@
       </c>
       <c r="S230" s="10"/>
     </row>
-    <row r="231" spans="1:19" ht="11" customHeight="1">
+    <row r="231" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A231" s="8" t="s">
         <v>87</v>
       </c>
@@ -14854,7 +14851,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="232" spans="1:19" ht="11" customHeight="1">
+    <row r="232" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A232" s="8" t="s">
         <v>87</v>
       </c>
@@ -14911,7 +14908,7 @@
       </c>
       <c r="S232" s="10"/>
     </row>
-    <row r="233" spans="1:19" ht="11" customHeight="1">
+    <row r="233" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A233" s="8" t="s">
         <v>87</v>
       </c>
@@ -14968,7 +14965,7 @@
       </c>
       <c r="S233" s="10"/>
     </row>
-    <row r="234" spans="1:19" ht="11" customHeight="1">
+    <row r="234" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A234" s="8" t="s">
         <v>87</v>
       </c>
@@ -15027,7 +15024,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="11" customHeight="1">
+    <row r="235" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A235" s="8" t="s">
         <v>87</v>
       </c>
@@ -15086,7 +15083,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="236" spans="1:19" ht="11" customHeight="1">
+    <row r="236" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A236" s="8" t="s">
         <v>87</v>
       </c>
@@ -15139,7 +15136,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="237" spans="1:19" ht="11" customHeight="1">
+    <row r="237" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A237" s="8" t="s">
         <v>87</v>
       </c>
@@ -15196,7 +15193,7 @@
       </c>
       <c r="S237" s="10"/>
     </row>
-    <row r="238" spans="1:19" ht="11" customHeight="1">
+    <row r="238" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A238" s="8" t="s">
         <v>87</v>
       </c>
@@ -15253,7 +15250,7 @@
       </c>
       <c r="S238" s="10"/>
     </row>
-    <row r="239" spans="1:19" ht="11" customHeight="1">
+    <row r="239" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A239" s="8" t="s">
         <v>87</v>
       </c>
@@ -15310,7 +15307,7 @@
       </c>
       <c r="S239" s="10"/>
     </row>
-    <row r="240" spans="1:19" ht="11" customHeight="1">
+    <row r="240" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A240" s="8" t="s">
         <v>87</v>
       </c>
@@ -15367,7 +15364,7 @@
       </c>
       <c r="S240" s="10"/>
     </row>
-    <row r="241" spans="1:19" ht="11" customHeight="1">
+    <row r="241" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A241" s="8" t="s">
         <v>87</v>
       </c>
@@ -15424,7 +15421,7 @@
       </c>
       <c r="S241" s="10"/>
     </row>
-    <row r="242" spans="1:19" ht="11" customHeight="1">
+    <row r="242" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A242" s="8" t="s">
         <v>87</v>
       </c>
@@ -15481,7 +15478,7 @@
       </c>
       <c r="S242" s="10"/>
     </row>
-    <row r="243" spans="1:19" ht="11" customHeight="1">
+    <row r="243" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A243" s="8" t="s">
         <v>87</v>
       </c>
@@ -15538,7 +15535,7 @@
       </c>
       <c r="S243" s="10"/>
     </row>
-    <row r="244" spans="1:19" ht="11" customHeight="1">
+    <row r="244" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A244" s="8" t="s">
         <v>87</v>
       </c>
@@ -15595,7 +15592,7 @@
       </c>
       <c r="S244" s="10"/>
     </row>
-    <row r="245" spans="1:19" ht="11" customHeight="1">
+    <row r="245" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A245" s="8" t="s">
         <v>87</v>
       </c>
@@ -15654,7 +15651,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="246" spans="1:19" ht="11" customHeight="1">
+    <row r="246" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A246" s="8" t="s">
         <v>87</v>
       </c>
@@ -15711,7 +15708,7 @@
       </c>
       <c r="S246" s="10"/>
     </row>
-    <row r="247" spans="1:19" ht="11" customHeight="1">
+    <row r="247" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A247" s="8" t="s">
         <v>87</v>
       </c>
@@ -15770,7 +15767,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="248" spans="1:19" ht="11" customHeight="1">
+    <row r="248" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A248" s="8" t="s">
         <v>87</v>
       </c>
@@ -15827,7 +15824,7 @@
       </c>
       <c r="S248" s="10"/>
     </row>
-    <row r="249" spans="1:19" ht="11" customHeight="1">
+    <row r="249" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A249" s="8" t="s">
         <v>87</v>
       </c>
@@ -15884,7 +15881,7 @@
       </c>
       <c r="S249" s="10"/>
     </row>
-    <row r="250" spans="1:19" ht="11" customHeight="1">
+    <row r="250" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A250" s="8" t="s">
         <v>87</v>
       </c>
@@ -15943,7 +15940,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="251" spans="1:19" ht="11" customHeight="1">
+    <row r="251" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A251" s="8" t="s">
         <v>87</v>
       </c>
@@ -16000,7 +15997,7 @@
       </c>
       <c r="S251" s="10"/>
     </row>
-    <row r="252" spans="1:19" ht="11" customHeight="1">
+    <row r="252" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A252" s="8" t="s">
         <v>87</v>
       </c>
@@ -16057,7 +16054,7 @@
       </c>
       <c r="S252" s="10"/>
     </row>
-    <row r="253" spans="1:19" ht="11" customHeight="1">
+    <row r="253" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A253" s="8" t="s">
         <v>87</v>
       </c>
@@ -16114,7 +16111,7 @@
       </c>
       <c r="S253" s="10"/>
     </row>
-    <row r="254" spans="1:19" ht="11" customHeight="1">
+    <row r="254" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A254" s="8" t="s">
         <v>87</v>
       </c>
@@ -16171,7 +16168,7 @@
       </c>
       <c r="S254" s="10"/>
     </row>
-    <row r="255" spans="1:19" ht="11" customHeight="1">
+    <row r="255" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A255" s="8" t="s">
         <v>87</v>
       </c>
@@ -16230,7 +16227,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="256" spans="1:19" ht="11" customHeight="1">
+    <row r="256" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A256" s="8" t="s">
         <v>87</v>
       </c>
@@ -16287,7 +16284,7 @@
       </c>
       <c r="S256" s="10"/>
     </row>
-    <row r="257" spans="1:19" ht="11" customHeight="1">
+    <row r="257" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A257" s="8" t="s">
         <v>87</v>
       </c>
@@ -16344,7 +16341,7 @@
       </c>
       <c r="S257" s="10"/>
     </row>
-    <row r="258" spans="1:19" ht="11" customHeight="1">
+    <row r="258" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A258" s="8" t="s">
         <v>87</v>
       </c>
@@ -16401,7 +16398,7 @@
       </c>
       <c r="S258" s="10"/>
     </row>
-    <row r="259" spans="1:19" ht="11" customHeight="1">
+    <row r="259" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A259" s="8" t="s">
         <v>87</v>
       </c>
@@ -16458,7 +16455,7 @@
       </c>
       <c r="S259" s="10"/>
     </row>
-    <row r="260" spans="1:19" ht="11" customHeight="1">
+    <row r="260" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A260" s="8" t="s">
         <v>87</v>
       </c>
@@ -16515,7 +16512,7 @@
       </c>
       <c r="S260" s="10"/>
     </row>
-    <row r="261" spans="1:19" ht="11" customHeight="1">
+    <row r="261" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A261" s="8" t="s">
         <v>87</v>
       </c>
@@ -16574,7 +16571,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="262" spans="1:19" ht="11" customHeight="1">
+    <row r="262" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A262" s="8" t="s">
         <v>87</v>
       </c>
@@ -16631,7 +16628,7 @@
       </c>
       <c r="S262" s="10"/>
     </row>
-    <row r="263" spans="1:19" ht="11" customHeight="1">
+    <row r="263" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A263" s="8" t="s">
         <v>87</v>
       </c>
@@ -16688,7 +16685,7 @@
       </c>
       <c r="S263" s="10"/>
     </row>
-    <row r="264" spans="1:19" ht="11" customHeight="1">
+    <row r="264" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A264" s="8" t="s">
         <v>87</v>
       </c>
@@ -16747,7 +16744,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="265" spans="1:19" ht="11" customHeight="1">
+    <row r="265" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A265" s="8" t="s">
         <v>87</v>
       </c>
@@ -16804,7 +16801,7 @@
       </c>
       <c r="S265" s="10"/>
     </row>
-    <row r="266" spans="1:19" ht="11" customHeight="1">
+    <row r="266" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A266" s="8" t="s">
         <v>87</v>
       </c>
@@ -16861,7 +16858,7 @@
       </c>
       <c r="S266" s="10"/>
     </row>
-    <row r="267" spans="1:19" ht="11" customHeight="1">
+    <row r="267" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A267" s="8" t="s">
         <v>87</v>
       </c>
@@ -16918,7 +16915,7 @@
       </c>
       <c r="S267" s="10"/>
     </row>
-    <row r="268" spans="1:19" ht="11" customHeight="1">
+    <row r="268" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A268" s="8" t="s">
         <v>87</v>
       </c>
@@ -16975,7 +16972,7 @@
       </c>
       <c r="S268" s="10"/>
     </row>
-    <row r="269" spans="1:19" ht="11" customHeight="1">
+    <row r="269" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A269" s="8" t="s">
         <v>87</v>
       </c>
@@ -17028,7 +17025,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="270" spans="1:19" ht="11" customHeight="1">
+    <row r="270" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A270" s="8" t="s">
         <v>87</v>
       </c>
@@ -17087,7 +17084,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="271" spans="1:19" ht="11" customHeight="1">
+    <row r="271" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A271" s="8" t="s">
         <v>87</v>
       </c>
@@ -17144,7 +17141,7 @@
       </c>
       <c r="S271" s="10"/>
     </row>
-    <row r="272" spans="1:19" ht="11" customHeight="1">
+    <row r="272" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A272" s="8" t="s">
         <v>87</v>
       </c>
@@ -17201,7 +17198,7 @@
       </c>
       <c r="S272" s="10"/>
     </row>
-    <row r="273" spans="1:19" ht="11" customHeight="1">
+    <row r="273" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A273" s="8" t="s">
         <v>87</v>
       </c>
@@ -17258,7 +17255,7 @@
       </c>
       <c r="S273" s="10"/>
     </row>
-    <row r="274" spans="1:19" ht="11" customHeight="1">
+    <row r="274" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A274" s="8" t="s">
         <v>87</v>
       </c>
@@ -17311,7 +17308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="275" spans="1:19" ht="11" customHeight="1">
+    <row r="275" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A275" s="8" t="s">
         <v>87</v>
       </c>
@@ -17370,7 +17367,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="276" spans="1:19" ht="11" customHeight="1">
+    <row r="276" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A276" s="8" t="s">
         <v>87</v>
       </c>
@@ -17427,7 +17424,7 @@
       </c>
       <c r="S276" s="10"/>
     </row>
-    <row r="277" spans="1:19" ht="11" customHeight="1">
+    <row r="277" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A277" s="8" t="s">
         <v>87</v>
       </c>
@@ -17480,7 +17477,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="11" customHeight="1">
+    <row r="278" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A278" s="8" t="s">
         <v>87</v>
       </c>
@@ -17537,7 +17534,7 @@
       </c>
       <c r="S278" s="10"/>
     </row>
-    <row r="279" spans="1:19" ht="11" customHeight="1">
+    <row r="279" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A279" s="8" t="s">
         <v>87</v>
       </c>
@@ -17596,7 +17593,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="280" spans="1:19" ht="11" customHeight="1">
+    <row r="280" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A280" s="8" t="s">
         <v>87</v>
       </c>
@@ -17649,7 +17646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="281" spans="1:19" ht="11" customHeight="1">
+    <row r="281" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A281" s="8" t="s">
         <v>87</v>
       </c>
@@ -17706,7 +17703,7 @@
       </c>
       <c r="S281" s="10"/>
     </row>
-    <row r="282" spans="1:19" ht="11" customHeight="1">
+    <row r="282" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A282" s="8" t="s">
         <v>87</v>
       </c>
@@ -17765,7 +17762,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="283" spans="1:19" ht="11" customHeight="1">
+    <row r="283" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A283" s="8" t="s">
         <v>87</v>
       </c>
@@ -17822,7 +17819,7 @@
       </c>
       <c r="S283" s="10"/>
     </row>
-    <row r="284" spans="1:19" ht="11" customHeight="1">
+    <row r="284" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A284" s="8" t="s">
         <v>87</v>
       </c>
@@ -17879,7 +17876,7 @@
       </c>
       <c r="S284" s="10"/>
     </row>
-    <row r="285" spans="1:19" ht="11" customHeight="1">
+    <row r="285" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A285" s="8" t="s">
         <v>87</v>
       </c>
@@ -17936,7 +17933,7 @@
       </c>
       <c r="S285" s="10"/>
     </row>
-    <row r="286" spans="1:19" ht="11" customHeight="1">
+    <row r="286" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A286" s="8" t="s">
         <v>87</v>
       </c>
@@ -17993,7 +17990,7 @@
       </c>
       <c r="S286" s="10"/>
     </row>
-    <row r="287" spans="1:19" ht="11" customHeight="1">
+    <row r="287" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A287" s="8" t="s">
         <v>87</v>
       </c>
@@ -18050,7 +18047,7 @@
       </c>
       <c r="S287" s="10"/>
     </row>
-    <row r="288" spans="1:19" ht="11" customHeight="1">
+    <row r="288" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A288" s="8" t="s">
         <v>87</v>
       </c>
@@ -18109,7 +18106,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="289" spans="1:19" ht="11" customHeight="1">
+    <row r="289" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A289" s="8" t="s">
         <v>87</v>
       </c>
@@ -18166,7 +18163,7 @@
       </c>
       <c r="S289" s="10"/>
     </row>
-    <row r="290" spans="1:19" ht="11" customHeight="1">
+    <row r="290" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A290" s="8" t="s">
         <v>124</v>
       </c>
@@ -18223,7 +18220,7 @@
       </c>
       <c r="S290" s="10"/>
     </row>
-    <row r="291" spans="1:19" ht="11" customHeight="1">
+    <row r="291" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A291" s="8" t="s">
         <v>124</v>
       </c>
@@ -18280,7 +18277,7 @@
       </c>
       <c r="S291" s="10"/>
     </row>
-    <row r="292" spans="1:19" ht="11" customHeight="1">
+    <row r="292" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A292" s="8" t="s">
         <v>124</v>
       </c>
@@ -18339,7 +18336,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="293" spans="1:19" ht="11" customHeight="1">
+    <row r="293" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A293" s="8" t="s">
         <v>124</v>
       </c>
@@ -18390,7 +18387,7 @@
       </c>
       <c r="S293" s="10"/>
     </row>
-    <row r="294" spans="1:19" ht="11" customHeight="1">
+    <row r="294" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A294" s="8" t="s">
         <v>124</v>
       </c>
@@ -18449,7 +18446,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="295" spans="1:19" ht="11" customHeight="1">
+    <row r="295" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A295" s="8" t="s">
         <v>124</v>
       </c>
@@ -18506,7 +18503,7 @@
       </c>
       <c r="S295" s="10"/>
     </row>
-    <row r="296" spans="1:19" ht="11" customHeight="1">
+    <row r="296" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A296" s="8" t="s">
         <v>124</v>
       </c>
@@ -18563,7 +18560,7 @@
       </c>
       <c r="S296" s="10"/>
     </row>
-    <row r="297" spans="1:19" ht="11" customHeight="1">
+    <row r="297" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A297" s="8" t="s">
         <v>124</v>
       </c>
@@ -18614,7 +18611,7 @@
       </c>
       <c r="S297" s="10"/>
     </row>
-    <row r="298" spans="1:19" ht="11" customHeight="1">
+    <row r="298" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A298" s="8" t="s">
         <v>124</v>
       </c>
@@ -18671,7 +18668,7 @@
       </c>
       <c r="S298" s="10"/>
     </row>
-    <row r="299" spans="1:19" ht="11" customHeight="1">
+    <row r="299" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A299" s="8" t="s">
         <v>124</v>
       </c>
@@ -18730,7 +18727,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="300" spans="1:19" ht="11" customHeight="1">
+    <row r="300" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A300" s="8" t="s">
         <v>124</v>
       </c>
@@ -18787,7 +18784,7 @@
       </c>
       <c r="S300" s="10"/>
     </row>
-    <row r="301" spans="1:19" ht="11" customHeight="1">
+    <row r="301" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A301" s="8" t="s">
         <v>124</v>
       </c>
@@ -18840,7 +18837,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="302" spans="1:19" ht="11" customHeight="1">
+    <row r="302" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A302" s="8" t="s">
         <v>124</v>
       </c>
@@ -18897,7 +18894,7 @@
       </c>
       <c r="S302" s="10"/>
     </row>
-    <row r="303" spans="1:19" ht="11" customHeight="1">
+    <row r="303" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A303" s="8" t="s">
         <v>124</v>
       </c>
@@ -18956,7 +18953,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="304" spans="1:19" ht="11" customHeight="1">
+    <row r="304" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A304" s="8" t="s">
         <v>124</v>
       </c>
@@ -19015,7 +19012,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="305" spans="1:19" ht="11" customHeight="1">
+    <row r="305" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A305" s="8" t="s">
         <v>124</v>
       </c>
@@ -19072,7 +19069,7 @@
       </c>
       <c r="S305" s="10"/>
     </row>
-    <row r="306" spans="1:19" ht="11" customHeight="1">
+    <row r="306" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A306" s="8" t="s">
         <v>124</v>
       </c>
@@ -19131,7 +19128,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="307" spans="1:19" ht="11" customHeight="1">
+    <row r="307" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A307" s="8" t="s">
         <v>124</v>
       </c>
@@ -19188,7 +19185,7 @@
       </c>
       <c r="S307" s="10"/>
     </row>
-    <row r="308" spans="1:19" ht="11" customHeight="1">
+    <row r="308" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A308" s="8" t="s">
         <v>124</v>
       </c>
@@ -19245,7 +19242,7 @@
       </c>
       <c r="S308" s="10"/>
     </row>
-    <row r="309" spans="1:19" ht="11" customHeight="1">
+    <row r="309" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A309" s="8" t="s">
         <v>124</v>
       </c>
@@ -19304,7 +19301,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="310" spans="1:19" ht="11" customHeight="1">
+    <row r="310" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A310" s="8" t="s">
         <v>124</v>
       </c>
@@ -19363,7 +19360,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="311" spans="1:19" ht="11" customHeight="1">
+    <row r="311" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A311" s="8" t="s">
         <v>124</v>
       </c>
@@ -19422,7 +19419,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="312" spans="1:19" ht="11" customHeight="1">
+    <row r="312" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A312" s="8" t="s">
         <v>124</v>
       </c>
@@ -19479,7 +19476,7 @@
       </c>
       <c r="S312" s="10"/>
     </row>
-    <row r="313" spans="1:19" ht="11" customHeight="1">
+    <row r="313" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A313" s="8" t="s">
         <v>124</v>
       </c>
@@ -19532,7 +19529,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="314" spans="1:19" ht="11" customHeight="1">
+    <row r="314" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A314" s="8" t="s">
         <v>124</v>
       </c>
@@ -19589,7 +19586,7 @@
       </c>
       <c r="S314" s="10"/>
     </row>
-    <row r="315" spans="1:19" ht="11" customHeight="1">
+    <row r="315" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A315" s="8" t="s">
         <v>124</v>
       </c>
@@ -19648,7 +19645,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="316" spans="1:19" ht="11" customHeight="1">
+    <row r="316" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A316" s="8" t="s">
         <v>124</v>
       </c>
@@ -19707,7 +19704,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="317" spans="1:19" ht="11" customHeight="1">
+    <row r="317" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A317" s="8" t="s">
         <v>124</v>
       </c>
@@ -19760,7 +19757,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="318" spans="1:19" ht="11" customHeight="1">
+    <row r="318" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A318" s="8" t="s">
         <v>124</v>
       </c>
@@ -19817,7 +19814,7 @@
       </c>
       <c r="S318" s="10"/>
     </row>
-    <row r="319" spans="1:19" ht="11" customHeight="1">
+    <row r="319" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A319" s="8" t="s">
         <v>124</v>
       </c>
@@ -19876,7 +19873,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="320" spans="1:19" ht="11" customHeight="1">
+    <row r="320" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A320" s="8" t="s">
         <v>124</v>
       </c>
@@ -19929,7 +19926,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="321" spans="1:19" ht="11" customHeight="1">
+    <row r="321" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A321" s="8" t="s">
         <v>124</v>
       </c>
@@ -19986,7 +19983,7 @@
       </c>
       <c r="S321" s="10"/>
     </row>
-    <row r="322" spans="1:19" ht="11" customHeight="1">
+    <row r="322" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A322" s="8" t="s">
         <v>124</v>
       </c>
@@ -20043,7 +20040,7 @@
       </c>
       <c r="S322" s="10"/>
     </row>
-    <row r="323" spans="1:19" ht="11" customHeight="1">
+    <row r="323" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A323" s="8" t="s">
         <v>124</v>
       </c>
@@ -20100,7 +20097,7 @@
       </c>
       <c r="S323" s="10"/>
     </row>
-    <row r="324" spans="1:19" ht="11" customHeight="1">
+    <row r="324" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A324" s="8" t="s">
         <v>124</v>
       </c>
@@ -20159,7 +20156,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="325" spans="1:19" ht="11" customHeight="1">
+    <row r="325" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A325" s="8" t="s">
         <v>124</v>
       </c>
@@ -20218,7 +20215,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="326" spans="1:19" ht="11" customHeight="1">
+    <row r="326" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A326" s="8" t="s">
         <v>124</v>
       </c>
@@ -20271,7 +20268,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="327" spans="1:19" ht="11" customHeight="1">
+    <row r="327" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A327" s="8" t="s">
         <v>124</v>
       </c>
@@ -20324,7 +20321,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="328" spans="1:19" ht="11" customHeight="1">
+    <row r="328" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A328" s="8" t="s">
         <v>124</v>
       </c>
@@ -20383,7 +20380,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="329" spans="1:19" ht="11" customHeight="1">
+    <row r="329" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A329" s="8" t="s">
         <v>124</v>
       </c>
@@ -20440,7 +20437,7 @@
       </c>
       <c r="S329" s="10"/>
     </row>
-    <row r="330" spans="1:19" ht="11" customHeight="1">
+    <row r="330" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A330" s="8" t="s">
         <v>124</v>
       </c>
@@ -20497,7 +20494,7 @@
       </c>
       <c r="S330" s="10"/>
     </row>
-    <row r="331" spans="1:19" ht="11" customHeight="1">
+    <row r="331" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A331" s="8" t="s">
         <v>124</v>
       </c>
@@ -20554,7 +20551,7 @@
       </c>
       <c r="S331" s="10"/>
     </row>
-    <row r="332" spans="1:19" ht="11" customHeight="1">
+    <row r="332" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A332" s="8" t="s">
         <v>124</v>
       </c>
@@ -20611,7 +20608,7 @@
       </c>
       <c r="S332" s="10"/>
     </row>
-    <row r="333" spans="1:19" ht="11" customHeight="1">
+    <row r="333" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A333" s="8" t="s">
         <v>124</v>
       </c>
@@ -20668,7 +20665,7 @@
       </c>
       <c r="S333" s="10"/>
     </row>
-    <row r="334" spans="1:19" ht="11" customHeight="1">
+    <row r="334" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A334" s="8" t="s">
         <v>124</v>
       </c>
@@ -20725,7 +20722,7 @@
       </c>
       <c r="S334" s="10"/>
     </row>
-    <row r="335" spans="1:19" ht="11" customHeight="1">
+    <row r="335" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A335" s="8" t="s">
         <v>124</v>
       </c>
@@ -20784,7 +20781,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="336" spans="1:19" ht="11" customHeight="1">
+    <row r="336" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A336" s="8" t="s">
         <v>124</v>
       </c>
@@ -20841,7 +20838,7 @@
       </c>
       <c r="S336" s="10"/>
     </row>
-    <row r="337" spans="1:19" ht="11" customHeight="1">
+    <row r="337" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A337" s="8" t="s">
         <v>124</v>
       </c>
@@ -20894,7 +20891,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="338" spans="1:19" ht="11" customHeight="1">
+    <row r="338" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A338" s="8" t="s">
         <v>124</v>
       </c>
@@ -20951,7 +20948,7 @@
       </c>
       <c r="S338" s="10"/>
     </row>
-    <row r="339" spans="1:19" ht="11" customHeight="1">
+    <row r="339" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A339" s="8" t="s">
         <v>124</v>
       </c>
@@ -21008,7 +21005,7 @@
       </c>
       <c r="S339" s="10"/>
     </row>
-    <row r="340" spans="1:19" ht="11" customHeight="1">
+    <row r="340" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A340" s="8" t="s">
         <v>124</v>
       </c>
@@ -21067,7 +21064,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="341" spans="1:19" ht="11" customHeight="1">
+    <row r="341" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A341" s="8" t="s">
         <v>124</v>
       </c>
@@ -21124,7 +21121,7 @@
       </c>
       <c r="S341" s="10"/>
     </row>
-    <row r="342" spans="1:19" ht="11" customHeight="1">
+    <row r="342" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A342" s="8" t="s">
         <v>124</v>
       </c>
@@ -21181,7 +21178,7 @@
       </c>
       <c r="S342" s="10"/>
     </row>
-    <row r="343" spans="1:19" ht="11" customHeight="1">
+    <row r="343" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A343" s="8" t="s">
         <v>124</v>
       </c>
@@ -21240,7 +21237,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="344" spans="1:19" ht="11" customHeight="1">
+    <row r="344" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A344" s="8" t="s">
         <v>124</v>
       </c>
@@ -21299,7 +21296,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="345" spans="1:19" ht="11" customHeight="1">
+    <row r="345" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A345" s="8" t="s">
         <v>124</v>
       </c>
@@ -21352,7 +21349,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="346" spans="1:19" ht="11" customHeight="1">
+    <row r="346" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A346" s="8" t="s">
         <v>124</v>
       </c>
@@ -21409,7 +21406,7 @@
       </c>
       <c r="S346" s="10"/>
     </row>
-    <row r="347" spans="1:19" ht="11" customHeight="1">
+    <row r="347" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A347" s="8" t="s">
         <v>124</v>
       </c>
@@ -21466,7 +21463,7 @@
       </c>
       <c r="S347" s="10"/>
     </row>
-    <row r="348" spans="1:19" ht="11" customHeight="1">
+    <row r="348" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A348" s="8" t="s">
         <v>124</v>
       </c>
@@ -21525,7 +21522,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="349" spans="1:19" ht="11" customHeight="1">
+    <row r="349" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A349" s="8" t="s">
         <v>124</v>
       </c>
@@ -21584,7 +21581,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="350" spans="1:19" ht="11" customHeight="1">
+    <row r="350" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A350" s="8" t="s">
         <v>124</v>
       </c>
@@ -21641,7 +21638,7 @@
       </c>
       <c r="S350" s="10"/>
     </row>
-    <row r="351" spans="1:19" ht="11" customHeight="1">
+    <row r="351" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A351" s="8" t="s">
         <v>124</v>
       </c>
@@ -21698,7 +21695,7 @@
       </c>
       <c r="S351" s="10"/>
     </row>
-    <row r="352" spans="1:19" ht="11" customHeight="1">
+    <row r="352" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A352" s="8" t="s">
         <v>124</v>
       </c>
@@ -21755,7 +21752,7 @@
       </c>
       <c r="S352" s="10"/>
     </row>
-    <row r="353" spans="1:19" ht="11" customHeight="1">
+    <row r="353" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A353" s="8" t="s">
         <v>124</v>
       </c>
@@ -21814,7 +21811,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="354" spans="1:19" ht="11" customHeight="1">
+    <row r="354" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A354" s="8" t="s">
         <v>124</v>
       </c>
@@ -21871,7 +21868,7 @@
       </c>
       <c r="S354" s="10"/>
     </row>
-    <row r="355" spans="1:19" ht="11" customHeight="1">
+    <row r="355" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A355" s="8" t="s">
         <v>124</v>
       </c>
@@ -21928,7 +21925,7 @@
       </c>
       <c r="S355" s="10"/>
     </row>
-    <row r="356" spans="1:19" ht="11" customHeight="1">
+    <row r="356" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A356" s="8" t="s">
         <v>124</v>
       </c>
@@ -21987,7 +21984,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="357" spans="1:19" ht="11" customHeight="1">
+    <row r="357" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A357" s="8" t="s">
         <v>124</v>
       </c>
@@ -22044,7 +22041,7 @@
       </c>
       <c r="S357" s="10"/>
     </row>
-    <row r="358" spans="1:19" ht="11" customHeight="1">
+    <row r="358" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A358" s="8" t="s">
         <v>124</v>
       </c>
@@ -22103,7 +22100,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="359" spans="1:19" ht="11" customHeight="1">
+    <row r="359" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A359" s="8" t="s">
         <v>124</v>
       </c>
@@ -22162,7 +22159,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="360" spans="1:19" ht="11" customHeight="1">
+    <row r="360" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A360" s="8" t="s">
         <v>124</v>
       </c>
@@ -22221,7 +22218,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="361" spans="1:19" ht="11" customHeight="1">
+    <row r="361" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A361" s="8" t="s">
         <v>124</v>
       </c>
@@ -22280,7 +22277,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="362" spans="1:19" ht="11" customHeight="1">
+    <row r="362" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A362" s="8" t="s">
         <v>124</v>
       </c>
@@ -22337,7 +22334,7 @@
       </c>
       <c r="S362" s="10"/>
     </row>
-    <row r="363" spans="1:19" ht="11" customHeight="1">
+    <row r="363" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A363" s="8" t="s">
         <v>124</v>
       </c>
@@ -22396,7 +22393,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="364" spans="1:19" ht="11" customHeight="1">
+    <row r="364" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A364" s="8" t="s">
         <v>124</v>
       </c>
@@ -22449,7 +22446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="365" spans="1:19" ht="11" customHeight="1">
+    <row r="365" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A365" s="8" t="s">
         <v>124</v>
       </c>
@@ -22502,7 +22499,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="366" spans="1:19" ht="11" customHeight="1">
+    <row r="366" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A366" s="8" t="s">
         <v>124</v>
       </c>
@@ -22555,7 +22552,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="367" spans="1:19" ht="11" customHeight="1">
+    <row r="367" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A367" s="8" t="s">
         <v>124</v>
       </c>
@@ -22614,7 +22611,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="368" spans="1:19" ht="11" customHeight="1">
+    <row r="368" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A368" s="8" t="s">
         <v>124</v>
       </c>
@@ -22671,7 +22668,7 @@
       </c>
       <c r="S368" s="10"/>
     </row>
-    <row r="369" spans="1:19" ht="11" customHeight="1">
+    <row r="369" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A369" s="8" t="s">
         <v>124</v>
       </c>
@@ -22730,7 +22727,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="370" spans="1:19" ht="11" customHeight="1">
+    <row r="370" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A370" s="8" t="s">
         <v>124</v>
       </c>
@@ -22789,7 +22786,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="371" spans="1:19" ht="11" customHeight="1">
+    <row r="371" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A371" s="8" t="s">
         <v>124</v>
       </c>
@@ -22846,7 +22843,7 @@
       </c>
       <c r="S371" s="10"/>
     </row>
-    <row r="372" spans="1:19" ht="11" customHeight="1">
+    <row r="372" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A372" s="8" t="s">
         <v>124</v>
       </c>
@@ -22903,7 +22900,7 @@
       </c>
       <c r="S372" s="10"/>
     </row>
-    <row r="373" spans="1:19" ht="11" customHeight="1">
+    <row r="373" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A373" s="8" t="s">
         <v>124</v>
       </c>
@@ -22956,7 +22953,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="374" spans="1:19" ht="11" customHeight="1">
+    <row r="374" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A374" s="8" t="s">
         <v>124</v>
       </c>
@@ -23009,7 +23006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="375" spans="1:19" ht="11" customHeight="1">
+    <row r="375" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A375" s="8" t="s">
         <v>124</v>
       </c>
@@ -23066,7 +23063,7 @@
       </c>
       <c r="S375" s="10"/>
     </row>
-    <row r="376" spans="1:19" ht="11" customHeight="1">
+    <row r="376" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A376" s="8" t="s">
         <v>124</v>
       </c>
@@ -23125,7 +23122,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="377" spans="1:19" ht="11" customHeight="1">
+    <row r="377" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A377" s="8" t="s">
         <v>124</v>
       </c>
@@ -23184,7 +23181,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="378" spans="1:19" ht="11" customHeight="1">
+    <row r="378" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A378" s="8" t="s">
         <v>124</v>
       </c>
@@ -23241,7 +23238,7 @@
       </c>
       <c r="S378" s="10"/>
     </row>
-    <row r="379" spans="1:19" ht="11" customHeight="1">
+    <row r="379" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A379" s="8" t="s">
         <v>124</v>
       </c>
@@ -23298,7 +23295,7 @@
       </c>
       <c r="S379" s="10"/>
     </row>
-    <row r="380" spans="1:19" ht="11" customHeight="1">
+    <row r="380" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A380" s="8" t="s">
         <v>124</v>
       </c>
@@ -23355,7 +23352,7 @@
       </c>
       <c r="S380" s="10"/>
     </row>
-    <row r="381" spans="1:19" ht="11" customHeight="1">
+    <row r="381" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A381" s="8" t="s">
         <v>124</v>
       </c>
@@ -23412,7 +23409,7 @@
       </c>
       <c r="S381" s="10"/>
     </row>
-    <row r="382" spans="1:19" ht="11" customHeight="1">
+    <row r="382" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A382" s="8" t="s">
         <v>124</v>
       </c>
@@ -23471,7 +23468,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="383" spans="1:19" ht="11" customHeight="1">
+    <row r="383" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A383" s="8" t="s">
         <v>124</v>
       </c>
@@ -23524,7 +23521,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="384" spans="1:19" ht="11" customHeight="1">
+    <row r="384" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A384" s="8" t="s">
         <v>124</v>
       </c>
@@ -23581,7 +23578,7 @@
       </c>
       <c r="S384" s="10"/>
     </row>
-    <row r="385" spans="1:19" ht="11" customHeight="1">
+    <row r="385" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A385" s="8" t="s">
         <v>124</v>
       </c>
@@ -23638,7 +23635,7 @@
       </c>
       <c r="S385" s="10"/>
     </row>
-    <row r="386" spans="1:19" ht="11" customHeight="1">
+    <row r="386" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A386" s="8" t="s">
         <v>124</v>
       </c>
@@ -23695,7 +23692,7 @@
       </c>
       <c r="S386" s="10"/>
     </row>
-    <row r="387" spans="1:19" ht="11" customHeight="1">
+    <row r="387" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A387" s="8" t="s">
         <v>124</v>
       </c>
@@ -23754,7 +23751,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="388" spans="1:19" ht="11" customHeight="1">
+    <row r="388" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A388" s="8" t="s">
         <v>124</v>
       </c>
@@ -23813,7 +23810,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="389" spans="1:19" ht="11" customHeight="1">
+    <row r="389" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A389" s="8" t="s">
         <v>124</v>
       </c>
@@ -23872,7 +23869,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="390" spans="1:19" ht="11" customHeight="1">
+    <row r="390" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A390" s="8" t="s">
         <v>124</v>
       </c>
@@ -23931,7 +23928,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="391" spans="1:19" ht="11" customHeight="1">
+    <row r="391" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A391" s="8" t="s">
         <v>124</v>
       </c>
@@ -23988,7 +23985,7 @@
       </c>
       <c r="S391" s="10"/>
     </row>
-    <row r="392" spans="1:19" ht="11" customHeight="1">
+    <row r="392" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A392" s="8" t="s">
         <v>124</v>
       </c>
@@ -24041,7 +24038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="393" spans="1:19" ht="11" customHeight="1">
+    <row r="393" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A393" s="8" t="s">
         <v>124</v>
       </c>
@@ -24094,7 +24091,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="394" spans="1:19" ht="11" customHeight="1">
+    <row r="394" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A394" s="8" t="s">
         <v>124</v>
       </c>
@@ -24147,7 +24144,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="395" spans="1:19" ht="11" customHeight="1">
+    <row r="395" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A395" s="8" t="s">
         <v>124</v>
       </c>
@@ -24206,7 +24203,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="396" spans="1:19" ht="11" customHeight="1">
+    <row r="396" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A396" s="8" t="s">
         <v>124</v>
       </c>
@@ -24265,7 +24262,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="397" spans="1:19" ht="11" customHeight="1">
+    <row r="397" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A397" s="8" t="s">
         <v>124</v>
       </c>
@@ -24324,7 +24321,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="398" spans="1:19" ht="11" customHeight="1">
+    <row r="398" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A398" s="8" t="s">
         <v>124</v>
       </c>
@@ -24377,7 +24374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="399" spans="1:19" ht="11" customHeight="1">
+    <row r="399" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A399" s="8" t="s">
         <v>124</v>
       </c>
@@ -24434,7 +24431,7 @@
       </c>
       <c r="S399" s="10"/>
     </row>
-    <row r="400" spans="1:19" ht="11" customHeight="1">
+    <row r="400" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A400" s="8" t="s">
         <v>124</v>
       </c>
@@ -24493,7 +24490,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="401" spans="1:19" ht="11" customHeight="1">
+    <row r="401" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A401" s="8" t="s">
         <v>124</v>
       </c>
@@ -24550,7 +24547,7 @@
       </c>
       <c r="S401" s="10"/>
     </row>
-    <row r="402" spans="1:19" ht="11" customHeight="1">
+    <row r="402" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A402" s="8" t="s">
         <v>124</v>
       </c>
@@ -24607,7 +24604,7 @@
       </c>
       <c r="S402" s="10"/>
     </row>
-    <row r="403" spans="1:19" ht="11" customHeight="1">
+    <row r="403" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A403" s="8" t="s">
         <v>124</v>
       </c>
@@ -24664,7 +24661,7 @@
       </c>
       <c r="S403" s="10"/>
     </row>
-    <row r="404" spans="1:19" ht="11" customHeight="1">
+    <row r="404" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A404" s="8" t="s">
         <v>124</v>
       </c>
@@ -24721,7 +24718,7 @@
       </c>
       <c r="S404" s="10"/>
     </row>
-    <row r="405" spans="1:19" ht="11" customHeight="1">
+    <row r="405" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A405" s="8" t="s">
         <v>124</v>
       </c>
@@ -24778,7 +24775,7 @@
       </c>
       <c r="S405" s="10"/>
     </row>
-    <row r="406" spans="1:19" ht="11" customHeight="1">
+    <row r="406" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A406" s="8" t="s">
         <v>124</v>
       </c>
@@ -24837,7 +24834,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="407" spans="1:19" ht="11" customHeight="1">
+    <row r="407" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A407" s="8" t="s">
         <v>124</v>
       </c>
@@ -24894,7 +24891,7 @@
       </c>
       <c r="S407" s="10"/>
     </row>
-    <row r="408" spans="1:19" ht="11" customHeight="1">
+    <row r="408" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A408" s="8" t="s">
         <v>124</v>
       </c>
@@ -24953,7 +24950,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="409" spans="1:19" ht="11" customHeight="1">
+    <row r="409" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A409" s="8" t="s">
         <v>124</v>
       </c>
@@ -25012,7 +25009,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="410" spans="1:19" ht="11" customHeight="1">
+    <row r="410" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A410" s="8" t="s">
         <v>124</v>
       </c>
@@ -25071,7 +25068,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="411" spans="1:19" ht="11" customHeight="1">
+    <row r="411" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A411" s="8" t="s">
         <v>124</v>
       </c>
@@ -25128,7 +25125,7 @@
       </c>
       <c r="S411" s="10"/>
     </row>
-    <row r="412" spans="1:19" ht="11" customHeight="1">
+    <row r="412" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A412" s="8" t="s">
         <v>124</v>
       </c>
@@ -25187,7 +25184,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="413" spans="1:19" ht="11" customHeight="1">
+    <row r="413" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A413" s="8" t="s">
         <v>124</v>
       </c>
@@ -25244,7 +25241,7 @@
       </c>
       <c r="S413" s="10"/>
     </row>
-    <row r="414" spans="1:19" ht="11" customHeight="1">
+    <row r="414" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A414" s="8" t="s">
         <v>124</v>
       </c>
@@ -25301,7 +25298,7 @@
       </c>
       <c r="S414" s="10"/>
     </row>
-    <row r="415" spans="1:19" ht="11" customHeight="1">
+    <row r="415" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A415" s="8" t="s">
         <v>124</v>
       </c>
@@ -25358,7 +25355,7 @@
       </c>
       <c r="S415" s="10"/>
     </row>
-    <row r="416" spans="1:19" ht="11" customHeight="1">
+    <row r="416" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A416" s="8" t="s">
         <v>124</v>
       </c>
@@ -25415,7 +25412,7 @@
       </c>
       <c r="S416" s="10"/>
     </row>
-    <row r="417" spans="1:19" ht="11" customHeight="1">
+    <row r="417" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A417" s="8" t="s">
         <v>124</v>
       </c>
@@ -25472,7 +25469,7 @@
       </c>
       <c r="S417" s="10"/>
     </row>
-    <row r="418" spans="1:19" ht="11" customHeight="1">
+    <row r="418" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A418" s="8" t="s">
         <v>124</v>
       </c>
@@ -25529,7 +25526,7 @@
       </c>
       <c r="S418" s="10"/>
     </row>
-    <row r="419" spans="1:19" ht="11" customHeight="1">
+    <row r="419" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A419" s="8" t="s">
         <v>124</v>
       </c>
@@ -25580,7 +25577,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="420" spans="1:19" ht="11" customHeight="1">
+    <row r="420" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A420" s="8" t="s">
         <v>124</v>
       </c>
@@ -25637,7 +25634,7 @@
       </c>
       <c r="S420" s="10"/>
     </row>
-    <row r="421" spans="1:19" ht="11" customHeight="1">
+    <row r="421" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A421" s="8" t="s">
         <v>124</v>
       </c>
@@ -25694,7 +25691,7 @@
       </c>
       <c r="S421" s="10"/>
     </row>
-    <row r="422" spans="1:19" ht="11" customHeight="1">
+    <row r="422" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A422" s="8" t="s">
         <v>124</v>
       </c>
@@ -25751,7 +25748,7 @@
       </c>
       <c r="S422" s="10"/>
     </row>
-    <row r="423" spans="1:19" ht="11" customHeight="1">
+    <row r="423" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A423" s="8" t="s">
         <v>124</v>
       </c>
@@ -25810,7 +25807,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="424" spans="1:19" ht="11" customHeight="1">
+    <row r="424" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A424" s="8" t="s">
         <v>124</v>
       </c>
@@ -25867,7 +25864,7 @@
       </c>
       <c r="S424" s="10"/>
     </row>
-    <row r="425" spans="1:19" ht="11" customHeight="1">
+    <row r="425" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A425" s="8" t="s">
         <v>124</v>
       </c>
@@ -25920,7 +25917,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="426" spans="1:19" ht="11" customHeight="1">
+    <row r="426" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A426" s="8" t="s">
         <v>124</v>
       </c>
@@ -25979,7 +25976,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="427" spans="1:19" ht="11" customHeight="1">
+    <row r="427" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A427" s="8" t="s">
         <v>124</v>
       </c>
@@ -26036,7 +26033,7 @@
       </c>
       <c r="S427" s="10"/>
     </row>
-    <row r="428" spans="1:19" ht="11" customHeight="1">
+    <row r="428" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A428" s="8" t="s">
         <v>124</v>
       </c>
@@ -26093,7 +26090,7 @@
       </c>
       <c r="S428" s="10"/>
     </row>
-    <row r="429" spans="1:19" ht="11" customHeight="1">
+    <row r="429" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A429" s="8" t="s">
         <v>124</v>
       </c>
@@ -26152,7 +26149,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="430" spans="1:19" ht="11" customHeight="1">
+    <row r="430" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A430" s="8" t="s">
         <v>124</v>
       </c>
@@ -26211,7 +26208,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="431" spans="1:19" ht="11" customHeight="1">
+    <row r="431" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A431" s="8" t="s">
         <v>124</v>
       </c>
@@ -26270,7 +26267,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="432" spans="1:19" ht="11" customHeight="1">
+    <row r="432" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A432" s="8" t="s">
         <v>124</v>
       </c>
@@ -26329,7 +26326,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="433" spans="1:19" ht="11" customHeight="1">
+    <row r="433" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A433" s="8" t="s">
         <v>124</v>
       </c>
@@ -26388,7 +26385,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="434" spans="1:19" ht="11" customHeight="1">
+    <row r="434" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A434" s="8" t="s">
         <v>124</v>
       </c>
@@ -26447,7 +26444,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="435" spans="1:19" ht="11" customHeight="1">
+    <row r="435" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A435" s="8" t="s">
         <v>124</v>
       </c>
@@ -26500,7 +26497,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="436" spans="1:19" ht="11" customHeight="1">
+    <row r="436" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A436" s="8" t="s">
         <v>124</v>
       </c>
@@ -26557,7 +26554,7 @@
       </c>
       <c r="S436" s="10"/>
     </row>
-    <row r="437" spans="1:19" ht="11" customHeight="1">
+    <row r="437" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A437" s="8" t="s">
         <v>124</v>
       </c>
@@ -26616,7 +26613,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="438" spans="1:19" ht="11" customHeight="1">
+    <row r="438" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A438" s="8" t="s">
         <v>124</v>
       </c>
@@ -26673,7 +26670,7 @@
       </c>
       <c r="S438" s="10"/>
     </row>
-    <row r="439" spans="1:19" ht="11" customHeight="1">
+    <row r="439" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A439" s="8" t="s">
         <v>124</v>
       </c>
@@ -26730,7 +26727,7 @@
       </c>
       <c r="S439" s="10"/>
     </row>
-    <row r="440" spans="1:19" ht="11" customHeight="1">
+    <row r="440" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A440" s="8" t="s">
         <v>124</v>
       </c>
@@ -26781,7 +26778,7 @@
       </c>
       <c r="S440" s="10"/>
     </row>
-    <row r="441" spans="1:19" ht="11" customHeight="1">
+    <row r="441" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A441" s="8" t="s">
         <v>124</v>
       </c>
@@ -26840,7 +26837,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="442" spans="1:19" ht="11" customHeight="1">
+    <row r="442" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A442" s="8" t="s">
         <v>124</v>
       </c>
@@ -26893,7 +26890,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="443" spans="1:19" ht="11" customHeight="1">
+    <row r="443" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A443" s="8" t="s">
         <v>124</v>
       </c>
@@ -26952,7 +26949,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="444" spans="1:19" ht="11" customHeight="1">
+    <row r="444" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A444" s="8" t="s">
         <v>124</v>
       </c>
@@ -27011,7 +27008,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="445" spans="1:19" ht="11" customHeight="1">
+    <row r="445" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A445" s="8" t="s">
         <v>124</v>
       </c>
@@ -27070,7 +27067,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="446" spans="1:19" ht="11" customHeight="1">
+    <row r="446" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A446" s="8" t="s">
         <v>124</v>
       </c>
@@ -27129,7 +27126,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="447" spans="1:19" ht="11" customHeight="1">
+    <row r="447" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A447" s="8" t="s">
         <v>124</v>
       </c>
@@ -27186,7 +27183,7 @@
       </c>
       <c r="S447" s="10"/>
     </row>
-    <row r="448" spans="1:19" ht="11" customHeight="1">
+    <row r="448" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A448" s="8" t="s">
         <v>124</v>
       </c>
@@ -27243,7 +27240,7 @@
       </c>
       <c r="S448" s="10"/>
     </row>
-    <row r="449" spans="1:19" ht="11" customHeight="1">
+    <row r="449" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A449" s="8" t="s">
         <v>124</v>
       </c>
@@ -27302,7 +27299,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="450" spans="1:19" ht="11" customHeight="1">
+    <row r="450" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A450" s="8" t="s">
         <v>124</v>
       </c>
@@ -27361,7 +27358,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="451" spans="1:19" ht="11" customHeight="1">
+    <row r="451" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A451" s="8" t="s">
         <v>124</v>
       </c>
@@ -27418,7 +27415,7 @@
       </c>
       <c r="S451" s="10"/>
     </row>
-    <row r="452" spans="1:19" ht="11" customHeight="1">
+    <row r="452" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A452" s="8" t="s">
         <v>124</v>
       </c>
@@ -27477,7 +27474,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="453" spans="1:19" ht="11" customHeight="1">
+    <row r="453" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A453" s="8" t="s">
         <v>124</v>
       </c>
@@ -27534,7 +27531,7 @@
       </c>
       <c r="S453" s="10"/>
     </row>
-    <row r="454" spans="1:19" ht="11" customHeight="1">
+    <row r="454" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A454" s="8" t="s">
         <v>124</v>
       </c>
@@ -27591,7 +27588,7 @@
       </c>
       <c r="S454" s="10"/>
     </row>
-    <row r="455" spans="1:19" ht="11" customHeight="1">
+    <row r="455" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A455" s="8" t="s">
         <v>124</v>
       </c>
@@ -27648,7 +27645,7 @@
       </c>
       <c r="S455" s="10"/>
     </row>
-    <row r="456" spans="1:19" ht="11" customHeight="1">
+    <row r="456" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A456" s="8" t="s">
         <v>124</v>
       </c>
@@ -27707,7 +27704,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="457" spans="1:19" ht="11" customHeight="1">
+    <row r="457" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A457" s="8" t="s">
         <v>144</v>
       </c>
@@ -27766,7 +27763,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="458" spans="1:19" ht="11" customHeight="1">
+    <row r="458" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A458" s="8" t="s">
         <v>144</v>
       </c>
@@ -27825,7 +27822,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="459" spans="1:19" ht="11" customHeight="1">
+    <row r="459" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A459" s="8" t="s">
         <v>144</v>
       </c>
@@ -27884,7 +27881,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="460" spans="1:19" ht="11" customHeight="1">
+    <row r="460" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A460" s="8" t="s">
         <v>144</v>
       </c>
@@ -27943,7 +27940,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="461" spans="1:19" ht="11" customHeight="1">
+    <row r="461" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A461" s="8" t="s">
         <v>144</v>
       </c>
@@ -28002,7 +27999,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="462" spans="1:19" ht="11" customHeight="1">
+    <row r="462" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A462" s="8" t="s">
         <v>144</v>
       </c>
@@ -28061,7 +28058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="463" spans="1:19" ht="11" customHeight="1">
+    <row r="463" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A463" s="8" t="s">
         <v>144</v>
       </c>
@@ -28118,7 +28115,7 @@
       </c>
       <c r="S463" s="10"/>
     </row>
-    <row r="464" spans="1:19" ht="11" customHeight="1">
+    <row r="464" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A464" s="8" t="s">
         <v>144</v>
       </c>
@@ -28177,7 +28174,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="465" spans="1:19" ht="11" customHeight="1">
+    <row r="465" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A465" s="8" t="s">
         <v>144</v>
       </c>
@@ -28236,7 +28233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="466" spans="1:19" ht="11" customHeight="1">
+    <row r="466" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A466" s="8" t="s">
         <v>144</v>
       </c>
@@ -28293,7 +28290,7 @@
       </c>
       <c r="S466" s="10"/>
     </row>
-    <row r="467" spans="1:19" ht="11" customHeight="1">
+    <row r="467" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A467" s="8" t="s">
         <v>144</v>
       </c>
@@ -28350,7 +28347,7 @@
       </c>
       <c r="S467" s="10"/>
     </row>
-    <row r="468" spans="1:19" ht="11" customHeight="1">
+    <row r="468" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A468" s="8" t="s">
         <v>144</v>
       </c>
@@ -28409,7 +28406,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="469" spans="1:19" ht="11" customHeight="1">
+    <row r="469" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A469" s="8" t="s">
         <v>144</v>
       </c>
@@ -28468,7 +28465,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="470" spans="1:19" ht="11" customHeight="1">
+    <row r="470" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A470" s="8" t="s">
         <v>144</v>
       </c>
@@ -28527,7 +28524,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="471" spans="1:19" ht="11" customHeight="1">
+    <row r="471" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A471" s="8" t="s">
         <v>144</v>
       </c>
@@ -28586,7 +28583,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="472" spans="1:19" ht="11" customHeight="1">
+    <row r="472" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A472" s="8" t="s">
         <v>144</v>
       </c>
@@ -28645,7 +28642,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="473" spans="1:19" ht="11" customHeight="1">
+    <row r="473" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A473" s="8" t="s">
         <v>144</v>
       </c>
@@ -28704,7 +28701,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="474" spans="1:19" ht="11" customHeight="1">
+    <row r="474" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A474" s="8" t="s">
         <v>144</v>
       </c>
@@ -28763,7 +28760,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="475" spans="1:19" ht="11" customHeight="1">
+    <row r="475" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A475" s="8" t="s">
         <v>144</v>
       </c>
@@ -28822,7 +28819,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="476" spans="1:19" ht="11" customHeight="1">
+    <row r="476" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A476" s="8" t="s">
         <v>144</v>
       </c>
@@ -28881,7 +28878,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="477" spans="1:19" ht="11" customHeight="1">
+    <row r="477" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A477" s="8" t="s">
         <v>144</v>
       </c>
@@ -28938,7 +28935,7 @@
       </c>
       <c r="S477" s="10"/>
     </row>
-    <row r="478" spans="1:19" ht="11" customHeight="1">
+    <row r="478" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A478" s="8" t="s">
         <v>144</v>
       </c>
@@ -28997,7 +28994,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="479" spans="1:19" ht="11" customHeight="1">
+    <row r="479" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A479" s="8" t="s">
         <v>144</v>
       </c>
@@ -29054,7 +29051,7 @@
       </c>
       <c r="S479" s="10"/>
     </row>
-    <row r="480" spans="1:19" ht="11" customHeight="1">
+    <row r="480" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A480" s="8" t="s">
         <v>144</v>
       </c>
@@ -29113,7 +29110,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="481" spans="1:19" ht="11" customHeight="1">
+    <row r="481" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A481" s="8" t="s">
         <v>144</v>
       </c>
@@ -29166,7 +29163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="482" spans="1:19" ht="11" customHeight="1">
+    <row r="482" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A482" s="8" t="s">
         <v>144</v>
       </c>
@@ -29225,7 +29222,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="483" spans="1:19" ht="11" customHeight="1">
+    <row r="483" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A483" s="8" t="s">
         <v>144</v>
       </c>
@@ -29284,7 +29281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="484" spans="1:19" ht="11" customHeight="1">
+    <row r="484" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A484" s="8" t="s">
         <v>144</v>
       </c>
@@ -29341,7 +29338,7 @@
       </c>
       <c r="S484" s="10"/>
     </row>
-    <row r="485" spans="1:19" ht="11" customHeight="1">
+    <row r="485" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A485" s="8" t="s">
         <v>144</v>
       </c>
@@ -29398,7 +29395,7 @@
       </c>
       <c r="S485" s="10"/>
     </row>
-    <row r="486" spans="1:19" ht="11" customHeight="1">
+    <row r="486" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A486" s="8" t="s">
         <v>144</v>
       </c>
@@ -29455,7 +29452,7 @@
       </c>
       <c r="S486" s="10"/>
     </row>
-    <row r="487" spans="1:19" ht="11" customHeight="1">
+    <row r="487" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A487" s="8" t="s">
         <v>144</v>
       </c>
@@ -29512,7 +29509,7 @@
       </c>
       <c r="S487" s="10"/>
     </row>
-    <row r="488" spans="1:19" ht="11" customHeight="1">
+    <row r="488" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A488" s="8" t="s">
         <v>144</v>
       </c>
@@ -29571,7 +29568,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="489" spans="1:19" ht="11" customHeight="1">
+    <row r="489" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A489" s="8" t="s">
         <v>144</v>
       </c>
@@ -29628,7 +29625,7 @@
       </c>
       <c r="S489" s="10"/>
     </row>
-    <row r="490" spans="1:19" ht="11" customHeight="1">
+    <row r="490" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A490" s="8" t="s">
         <v>144</v>
       </c>
@@ -29687,7 +29684,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="491" spans="1:19" ht="11" customHeight="1">
+    <row r="491" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A491" s="8" t="s">
         <v>144</v>
       </c>
@@ -29740,7 +29737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="492" spans="1:19" ht="11" customHeight="1">
+    <row r="492" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A492" s="8" t="s">
         <v>144</v>
       </c>
@@ -29797,7 +29794,7 @@
       </c>
       <c r="S492" s="10"/>
     </row>
-    <row r="493" spans="1:19" ht="11" customHeight="1">
+    <row r="493" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A493" s="8" t="s">
         <v>144</v>
       </c>
@@ -29850,7 +29847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="494" spans="1:19" ht="11" customHeight="1">
+    <row r="494" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A494" s="8" t="s">
         <v>144</v>
       </c>
@@ -29909,7 +29906,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="495" spans="1:19" ht="11" customHeight="1">
+    <row r="495" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A495" s="8" t="s">
         <v>144</v>
       </c>
@@ -29968,7 +29965,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="496" spans="1:19" ht="11" customHeight="1">
+    <row r="496" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A496" s="8" t="s">
         <v>144</v>
       </c>
@@ -30025,7 +30022,7 @@
       </c>
       <c r="S496" s="10"/>
     </row>
-    <row r="497" spans="1:19" ht="11" customHeight="1">
+    <row r="497" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A497" s="8" t="s">
         <v>144</v>
       </c>
@@ -30078,7 +30075,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="498" spans="1:19" ht="11" customHeight="1">
+    <row r="498" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A498" s="8" t="s">
         <v>144</v>
       </c>
@@ -30137,7 +30134,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="499" spans="1:19" ht="11" customHeight="1">
+    <row r="499" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A499" s="8" t="s">
         <v>144</v>
       </c>
@@ -30194,7 +30191,7 @@
       </c>
       <c r="S499" s="10"/>
     </row>
-    <row r="500" spans="1:19" ht="11" customHeight="1">
+    <row r="500" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A500" s="8" t="s">
         <v>144</v>
       </c>
@@ -30247,7 +30244,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="501" spans="1:19" ht="11" customHeight="1">
+    <row r="501" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A501" s="8" t="s">
         <v>144</v>
       </c>
@@ -30306,7 +30303,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="502" spans="1:19" ht="11" customHeight="1">
+    <row r="502" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A502" s="8" t="s">
         <v>144</v>
       </c>
@@ -30363,7 +30360,7 @@
       </c>
       <c r="S502" s="10"/>
     </row>
-    <row r="503" spans="1:19" ht="11" customHeight="1">
+    <row r="503" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A503" s="8" t="s">
         <v>144</v>
       </c>
@@ -30416,7 +30413,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="504" spans="1:19" ht="11" customHeight="1">
+    <row r="504" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A504" s="8" t="s">
         <v>144</v>
       </c>
@@ -30473,7 +30470,7 @@
       </c>
       <c r="S504" s="10"/>
     </row>
-    <row r="505" spans="1:19" ht="11" customHeight="1">
+    <row r="505" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A505" s="8" t="s">
         <v>144</v>
       </c>
@@ -30532,7 +30529,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="506" spans="1:19" ht="11" customHeight="1">
+    <row r="506" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A506" s="8" t="s">
         <v>144</v>
       </c>
@@ -30589,7 +30586,7 @@
       </c>
       <c r="S506" s="10"/>
     </row>
-    <row r="507" spans="1:19" ht="11" customHeight="1">
+    <row r="507" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A507" s="8" t="s">
         <v>144</v>
       </c>
@@ -30648,7 +30645,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="508" spans="1:19" ht="11" customHeight="1">
+    <row r="508" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A508" s="8" t="s">
         <v>144</v>
       </c>
@@ -30707,7 +30704,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="509" spans="1:19" ht="11" customHeight="1">
+    <row r="509" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A509" s="8" t="s">
         <v>144</v>
       </c>
@@ -30764,7 +30761,7 @@
       </c>
       <c r="S509" s="10"/>
     </row>
-    <row r="510" spans="1:19" ht="11" customHeight="1">
+    <row r="510" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A510" s="8" t="s">
         <v>144</v>
       </c>
@@ -30823,7 +30820,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="511" spans="1:19" ht="11" customHeight="1">
+    <row r="511" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A511" s="8" t="s">
         <v>144</v>
       </c>
@@ -30880,7 +30877,7 @@
       </c>
       <c r="S511" s="10"/>
     </row>
-    <row r="512" spans="1:19" ht="11" customHeight="1">
+    <row r="512" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A512" s="8" t="s">
         <v>144</v>
       </c>
@@ -30937,7 +30934,7 @@
       </c>
       <c r="S512" s="10"/>
     </row>
-    <row r="513" spans="1:19" ht="11" customHeight="1">
+    <row r="513" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A513" s="8" t="s">
         <v>144</v>
       </c>
@@ -30990,7 +30987,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="514" spans="1:19" ht="11" customHeight="1">
+    <row r="514" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A514" s="8" t="s">
         <v>144</v>
       </c>
@@ -31049,7 +31046,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="515" spans="1:19" ht="11" customHeight="1">
+    <row r="515" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A515" s="8" t="s">
         <v>144</v>
       </c>
@@ -31108,7 +31105,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="516" spans="1:19" ht="11" customHeight="1">
+    <row r="516" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A516" s="8" t="s">
         <v>144</v>
       </c>
@@ -31161,7 +31158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="517" spans="1:19" ht="11" customHeight="1">
+    <row r="517" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A517" s="8" t="s">
         <v>144</v>
       </c>
@@ -31220,7 +31217,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="518" spans="1:19" ht="11" customHeight="1">
+    <row r="518" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A518" s="8" t="s">
         <v>144</v>
       </c>
@@ -31279,7 +31276,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="519" spans="1:19" ht="11" customHeight="1">
+    <row r="519" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A519" s="8" t="s">
         <v>144</v>
       </c>
@@ -31336,7 +31333,7 @@
       </c>
       <c r="S519" s="10"/>
     </row>
-    <row r="520" spans="1:19" ht="11" customHeight="1">
+    <row r="520" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A520" s="8" t="s">
         <v>144</v>
       </c>
@@ -31395,7 +31392,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="521" spans="1:19" ht="11" customHeight="1">
+    <row r="521" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A521" s="8" t="s">
         <v>144</v>
       </c>
@@ -31454,7 +31451,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="522" spans="1:19" ht="11" customHeight="1">
+    <row r="522" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A522" s="8" t="s">
         <v>144</v>
       </c>
@@ -31511,7 +31508,7 @@
       </c>
       <c r="S522" s="10"/>
     </row>
-    <row r="523" spans="1:19" ht="11" customHeight="1">
+    <row r="523" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A523" s="8" t="s">
         <v>144</v>
       </c>
@@ -31568,7 +31565,7 @@
       </c>
       <c r="S523" s="10"/>
     </row>
-    <row r="524" spans="1:19" ht="11" customHeight="1">
+    <row r="524" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A524" s="8" t="s">
         <v>144</v>
       </c>
@@ -31627,7 +31624,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="525" spans="1:19" ht="11" customHeight="1">
+    <row r="525" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A525" s="8" t="s">
         <v>144</v>
       </c>
@@ -31686,7 +31683,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="526" spans="1:19" ht="11" customHeight="1">
+    <row r="526" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A526" s="8" t="s">
         <v>144</v>
       </c>
@@ -31739,7 +31736,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="527" spans="1:19" ht="11" customHeight="1">
+    <row r="527" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A527" s="8" t="s">
         <v>144</v>
       </c>
@@ -31792,7 +31789,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="528" spans="1:19" ht="11" customHeight="1">
+    <row r="528" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A528" s="8" t="s">
         <v>144</v>
       </c>
@@ -31845,7 +31842,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="529" spans="1:19" ht="11" customHeight="1">
+    <row r="529" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A529" s="8" t="s">
         <v>144</v>
       </c>
@@ -31898,7 +31895,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="530" spans="1:19" ht="11" customHeight="1">
+    <row r="530" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A530" s="8" t="s">
         <v>144</v>
       </c>
@@ -31951,7 +31948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="531" spans="1:19" ht="11" customHeight="1">
+    <row r="531" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A531" s="8" t="s">
         <v>144</v>
       </c>
@@ -32010,7 +32007,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="532" spans="1:19" ht="11" customHeight="1">
+    <row r="532" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A532" s="8" t="s">
         <v>144</v>
       </c>
@@ -32067,7 +32064,7 @@
       </c>
       <c r="S532" s="10"/>
     </row>
-    <row r="533" spans="1:19" ht="11" customHeight="1">
+    <row r="533" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A533" s="8" t="s">
         <v>144</v>
       </c>
@@ -32126,7 +32123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="534" spans="1:19" ht="11" customHeight="1">
+    <row r="534" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A534" s="8" t="s">
         <v>144</v>
       </c>
@@ -32185,7 +32182,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="535" spans="1:19" ht="11" customHeight="1">
+    <row r="535" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A535" s="8" t="s">
         <v>144</v>
       </c>
@@ -32242,7 +32239,7 @@
       </c>
       <c r="S535" s="10"/>
     </row>
-    <row r="536" spans="1:19" ht="11" customHeight="1">
+    <row r="536" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A536" s="8" t="s">
         <v>144</v>
       </c>
@@ -32299,7 +32296,7 @@
       </c>
       <c r="S536" s="10"/>
     </row>
-    <row r="537" spans="1:19" ht="11" customHeight="1">
+    <row r="537" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A537" s="8" t="s">
         <v>144</v>
       </c>
@@ -32356,7 +32353,7 @@
       </c>
       <c r="S537" s="10"/>
     </row>
-    <row r="538" spans="1:19" ht="11" customHeight="1">
+    <row r="538" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A538" s="8" t="s">
         <v>144</v>
       </c>
@@ -32413,7 +32410,7 @@
       </c>
       <c r="S538" s="10"/>
     </row>
-    <row r="539" spans="1:19" ht="11" customHeight="1">
+    <row r="539" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A539" s="8" t="s">
         <v>144</v>
       </c>
@@ -32470,7 +32467,7 @@
       </c>
       <c r="S539" s="10"/>
     </row>
-    <row r="540" spans="1:19" ht="11" customHeight="1">
+    <row r="540" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A540" s="8" t="s">
         <v>144</v>
       </c>
@@ -32529,7 +32526,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="541" spans="1:19" ht="11" customHeight="1">
+    <row r="541" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A541" s="8" t="s">
         <v>144</v>
       </c>
@@ -32586,7 +32583,7 @@
       </c>
       <c r="S541" s="10"/>
     </row>
-    <row r="542" spans="1:19" ht="11" customHeight="1">
+    <row r="542" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A542" s="8" t="s">
         <v>144</v>
       </c>
@@ -32645,7 +32642,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="543" spans="1:19" ht="11" customHeight="1">
+    <row r="543" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A543" s="8" t="s">
         <v>144</v>
       </c>
@@ -32704,7 +32701,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="544" spans="1:19" ht="11" customHeight="1">
+    <row r="544" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A544" s="8" t="s">
         <v>144</v>
       </c>
@@ -32763,7 +32760,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="545" spans="1:19" ht="11" customHeight="1">
+    <row r="545" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A545" s="8" t="s">
         <v>144</v>
       </c>
@@ -32822,7 +32819,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="546" spans="1:19" ht="11" customHeight="1">
+    <row r="546" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A546" s="8" t="s">
         <v>144</v>
       </c>
@@ -32881,7 +32878,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="547" spans="1:19" ht="11" customHeight="1">
+    <row r="547" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A547" s="8" t="s">
         <v>144</v>
       </c>
@@ -32940,7 +32937,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="548" spans="1:19" ht="11" customHeight="1">
+    <row r="548" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A548" s="8" t="s">
         <v>144</v>
       </c>
@@ -32999,7 +32996,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="549" spans="1:19" ht="11" customHeight="1">
+    <row r="549" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A549" s="8" t="s">
         <v>144</v>
       </c>
@@ -33058,7 +33055,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="550" spans="1:19" ht="11" customHeight="1">
+    <row r="550" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A550" s="8" t="s">
         <v>144</v>
       </c>
@@ -33115,7 +33112,7 @@
       </c>
       <c r="S550" s="10"/>
     </row>
-    <row r="551" spans="1:19" ht="11" customHeight="1">
+    <row r="551" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A551" s="8" t="s">
         <v>144</v>
       </c>
@@ -33172,7 +33169,7 @@
       </c>
       <c r="S551" s="10"/>
     </row>
-    <row r="552" spans="1:19" ht="11" customHeight="1">
+    <row r="552" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A552" s="8" t="s">
         <v>144</v>
       </c>
@@ -33231,7 +33228,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="553" spans="1:19" ht="11" customHeight="1">
+    <row r="553" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A553" s="8" t="s">
         <v>144</v>
       </c>
@@ -33290,7 +33287,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="554" spans="1:19" ht="11" customHeight="1">
+    <row r="554" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A554" s="8" t="s">
         <v>144</v>
       </c>
@@ -33347,7 +33344,7 @@
       </c>
       <c r="S554" s="10"/>
     </row>
-    <row r="555" spans="1:19" ht="11" customHeight="1">
+    <row r="555" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A555" s="8" t="s">
         <v>144</v>
       </c>
@@ -33406,7 +33403,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="556" spans="1:19" ht="11" customHeight="1">
+    <row r="556" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A556" s="8" t="s">
         <v>144</v>
       </c>
@@ -33459,7 +33456,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="557" spans="1:19" ht="11" customHeight="1">
+    <row r="557" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A557" s="8" t="s">
         <v>144</v>
       </c>
@@ -33512,7 +33509,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="558" spans="1:19" ht="11" customHeight="1">
+    <row r="558" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A558" s="8" t="s">
         <v>144</v>
       </c>
@@ -33571,7 +33568,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="559" spans="1:19" ht="11" customHeight="1">
+    <row r="559" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A559" s="8" t="s">
         <v>144</v>
       </c>
@@ -33628,7 +33625,7 @@
       </c>
       <c r="S559" s="10"/>
     </row>
-    <row r="560" spans="1:19" ht="11" customHeight="1">
+    <row r="560" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A560" s="8" t="s">
         <v>144</v>
       </c>
@@ -33687,7 +33684,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="561" spans="1:19" ht="11" customHeight="1">
+    <row r="561" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A561" s="8" t="s">
         <v>144</v>
       </c>
@@ -33746,7 +33743,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="562" spans="1:19" ht="11" customHeight="1">
+    <row r="562" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A562" s="8" t="s">
         <v>144</v>
       </c>
@@ -33805,7 +33802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="563" spans="1:19" ht="11" customHeight="1">
+    <row r="563" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A563" s="8" t="s">
         <v>144</v>
       </c>
@@ -33862,7 +33859,7 @@
       </c>
       <c r="S563" s="10"/>
     </row>
-    <row r="564" spans="1:19" ht="11" customHeight="1">
+    <row r="564" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A564" s="8" t="s">
         <v>144</v>
       </c>
@@ -33921,7 +33918,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="565" spans="1:19" ht="11" customHeight="1">
+    <row r="565" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A565" s="8" t="s">
         <v>144</v>
       </c>
@@ -33980,7 +33977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="566" spans="1:19" ht="11" customHeight="1">
+    <row r="566" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A566" s="8" t="s">
         <v>144</v>
       </c>
@@ -34039,7 +34036,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="567" spans="1:19" ht="11" customHeight="1">
+    <row r="567" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A567" s="8" t="s">
         <v>170</v>
       </c>
@@ -34098,7 +34095,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="568" spans="1:19" ht="11" customHeight="1">
+    <row r="568" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A568" s="8" t="s">
         <v>170</v>
       </c>
@@ -34155,7 +34152,7 @@
       </c>
       <c r="S568" s="10"/>
     </row>
-    <row r="569" spans="1:19" ht="11" customHeight="1">
+    <row r="569" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A569" s="8" t="s">
         <v>170</v>
       </c>
@@ -34212,7 +34209,7 @@
       </c>
       <c r="S569" s="10"/>
     </row>
-    <row r="570" spans="1:19" ht="11" customHeight="1">
+    <row r="570" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A570" s="8" t="s">
         <v>170</v>
       </c>
@@ -34269,7 +34266,7 @@
       </c>
       <c r="S570" s="10"/>
     </row>
-    <row r="571" spans="1:19" ht="11" customHeight="1">
+    <row r="571" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A571" s="8" t="s">
         <v>170</v>
       </c>
@@ -34326,7 +34323,7 @@
       </c>
       <c r="S571" s="10"/>
     </row>
-    <row r="572" spans="1:19" ht="11" customHeight="1">
+    <row r="572" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A572" s="8" t="s">
         <v>170</v>
       </c>
@@ -34383,7 +34380,7 @@
       </c>
       <c r="S572" s="10"/>
     </row>
-    <row r="573" spans="1:19" ht="11" customHeight="1">
+    <row r="573" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A573" s="8" t="s">
         <v>170</v>
       </c>
@@ -34440,7 +34437,7 @@
       </c>
       <c r="S573" s="10"/>
     </row>
-    <row r="574" spans="1:19" ht="11" customHeight="1">
+    <row r="574" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A574" s="8" t="s">
         <v>170</v>
       </c>
@@ -34497,7 +34494,7 @@
       </c>
       <c r="S574" s="10"/>
     </row>
-    <row r="575" spans="1:19" ht="11" customHeight="1">
+    <row r="575" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A575" s="8" t="s">
         <v>170</v>
       </c>
@@ -34554,7 +34551,7 @@
       </c>
       <c r="S575" s="10"/>
     </row>
-    <row r="576" spans="1:19" ht="11" customHeight="1">
+    <row r="576" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A576" s="8" t="s">
         <v>170</v>
       </c>
@@ -34611,7 +34608,7 @@
       </c>
       <c r="S576" s="10"/>
     </row>
-    <row r="577" spans="1:19" ht="11" customHeight="1">
+    <row r="577" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A577" s="8" t="s">
         <v>170</v>
       </c>
@@ -34670,7 +34667,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="578" spans="1:19" ht="11" customHeight="1">
+    <row r="578" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A578" s="8" t="s">
         <v>170</v>
       </c>
@@ -34727,7 +34724,7 @@
       </c>
       <c r="S578" s="10"/>
     </row>
-    <row r="579" spans="1:19" ht="11" customHeight="1">
+    <row r="579" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A579" s="8" t="s">
         <v>170</v>
       </c>
@@ -34784,7 +34781,7 @@
       </c>
       <c r="S579" s="10"/>
     </row>
-    <row r="580" spans="1:19" ht="11" customHeight="1">
+    <row r="580" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A580" s="8" t="s">
         <v>170</v>
       </c>
@@ -34841,7 +34838,7 @@
       </c>
       <c r="S580" s="10"/>
     </row>
-    <row r="581" spans="1:19" ht="11" customHeight="1">
+    <row r="581" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A581" s="8" t="s">
         <v>170</v>
       </c>
@@ -34898,7 +34895,7 @@
       </c>
       <c r="S581" s="10"/>
     </row>
-    <row r="582" spans="1:19" ht="11" customHeight="1">
+    <row r="582" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A582" s="8" t="s">
         <v>170</v>
       </c>
@@ -34957,7 +34954,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="583" spans="1:19" ht="11" customHeight="1">
+    <row r="583" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A583" s="8" t="s">
         <v>170</v>
       </c>
@@ -35016,7 +35013,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="584" spans="1:19" ht="11" customHeight="1">
+    <row r="584" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A584" s="8" t="s">
         <v>170</v>
       </c>
@@ -35075,7 +35072,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="585" spans="1:19" ht="11" customHeight="1">
+    <row r="585" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A585" s="8" t="s">
         <v>170</v>
       </c>
@@ -35132,7 +35129,7 @@
       </c>
       <c r="S585" s="10"/>
     </row>
-    <row r="586" spans="1:19" ht="11" customHeight="1">
+    <row r="586" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A586" s="8" t="s">
         <v>170</v>
       </c>
@@ -35191,7 +35188,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="587" spans="1:19" ht="11" customHeight="1">
+    <row r="587" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A587" s="8" t="s">
         <v>170</v>
       </c>
@@ -35248,7 +35245,7 @@
       </c>
       <c r="S587" s="10"/>
     </row>
-    <row r="588" spans="1:19" ht="11" customHeight="1">
+    <row r="588" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A588" s="8" t="s">
         <v>170</v>
       </c>
@@ -35305,7 +35302,7 @@
       </c>
       <c r="S588" s="10"/>
     </row>
-    <row r="589" spans="1:19" ht="11" customHeight="1">
+    <row r="589" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A589" s="8" t="s">
         <v>170</v>
       </c>
@@ -35364,7 +35361,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="590" spans="1:19" ht="11" customHeight="1">
+    <row r="590" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A590" s="8" t="s">
         <v>170</v>
       </c>
@@ -35423,7 +35420,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="591" spans="1:19" ht="11" customHeight="1">
+    <row r="591" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A591" s="8" t="s">
         <v>170</v>
       </c>
@@ -35480,7 +35477,7 @@
       </c>
       <c r="S591" s="10"/>
     </row>
-    <row r="592" spans="1:19" ht="11" customHeight="1">
+    <row r="592" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A592" s="8" t="s">
         <v>170</v>
       </c>
@@ -35539,7 +35536,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="593" spans="1:19" ht="11" customHeight="1">
+    <row r="593" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A593" s="8" t="s">
         <v>170</v>
       </c>
@@ -35598,7 +35595,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="594" spans="1:19" ht="11" customHeight="1">
+    <row r="594" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A594" s="8" t="s">
         <v>170</v>
       </c>
@@ -35657,7 +35654,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="595" spans="1:19" ht="11" customHeight="1">
+    <row r="595" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A595" s="8" t="s">
         <v>170</v>
       </c>
@@ -35716,7 +35713,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="596" spans="1:19" ht="11" customHeight="1">
+    <row r="596" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A596" s="8" t="s">
         <v>170</v>
       </c>
@@ -35773,7 +35770,7 @@
       </c>
       <c r="S596" s="10"/>
     </row>
-    <row r="597" spans="1:19" ht="11" customHeight="1">
+    <row r="597" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A597" s="8" t="s">
         <v>170</v>
       </c>
@@ -35832,7 +35829,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="598" spans="1:19" ht="11" customHeight="1">
+    <row r="598" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A598" s="8" t="s">
         <v>170</v>
       </c>
@@ -35885,7 +35882,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="599" spans="1:19" ht="11" customHeight="1">
+    <row r="599" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A599" s="8" t="s">
         <v>170</v>
       </c>
@@ -35938,7 +35935,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="600" spans="1:19" ht="11" customHeight="1">
+    <row r="600" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A600" s="8" t="s">
         <v>170</v>
       </c>
@@ -35997,7 +35994,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="601" spans="1:19" ht="11" customHeight="1">
+    <row r="601" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A601" s="8" t="s">
         <v>170</v>
       </c>
@@ -36054,7 +36051,7 @@
       </c>
       <c r="S601" s="10"/>
     </row>
-    <row r="602" spans="1:19" ht="11" customHeight="1">
+    <row r="602" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A602" s="8" t="s">
         <v>170</v>
       </c>
@@ -36113,7 +36110,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="603" spans="1:19" ht="11" customHeight="1">
+    <row r="603" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A603" s="8" t="s">
         <v>170</v>
       </c>
@@ -36172,7 +36169,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="604" spans="1:19" ht="11" customHeight="1">
+    <row r="604" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A604" s="8" t="s">
         <v>170</v>
       </c>
@@ -36231,7 +36228,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="605" spans="1:19" ht="11" customHeight="1">
+    <row r="605" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A605" s="8" t="s">
         <v>170</v>
       </c>
@@ -36290,7 +36287,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="606" spans="1:19" ht="11" customHeight="1">
+    <row r="606" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A606" s="8" t="s">
         <v>170</v>
       </c>
@@ -36349,7 +36346,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="607" spans="1:19" ht="11" customHeight="1">
+    <row r="607" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A607" s="8" t="s">
         <v>170</v>
       </c>
@@ -36408,7 +36405,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="608" spans="1:19" ht="11" customHeight="1">
+    <row r="608" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A608" s="8" t="s">
         <v>170</v>
       </c>
@@ -36467,7 +36464,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="609" spans="1:19" ht="11" customHeight="1">
+    <row r="609" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A609" s="8" t="s">
         <v>170</v>
       </c>
@@ -36520,7 +36517,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="610" spans="1:19" ht="11" customHeight="1">
+    <row r="610" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A610" s="8" t="s">
         <v>170</v>
       </c>
@@ -36577,7 +36574,7 @@
       </c>
       <c r="S610" s="10"/>
     </row>
-    <row r="611" spans="1:19" ht="11" customHeight="1">
+    <row r="611" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A611" s="8" t="s">
         <v>170</v>
       </c>
@@ -36636,7 +36633,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="612" spans="1:19" ht="11" customHeight="1">
+    <row r="612" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A612" s="8" t="s">
         <v>170</v>
       </c>
@@ -36693,7 +36690,7 @@
       </c>
       <c r="S612" s="10"/>
     </row>
-    <row r="613" spans="1:19" ht="11" customHeight="1">
+    <row r="613" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A613" s="8" t="s">
         <v>170</v>
       </c>
@@ -36750,7 +36747,7 @@
       </c>
       <c r="S613" s="10"/>
     </row>
-    <row r="614" spans="1:19" ht="11" customHeight="1">
+    <row r="614" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A614" s="8" t="s">
         <v>170</v>
       </c>
@@ -36807,7 +36804,7 @@
       </c>
       <c r="S614" s="10"/>
     </row>
-    <row r="615" spans="1:19" ht="11" customHeight="1">
+    <row r="615" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A615" s="8" t="s">
         <v>170</v>
       </c>
@@ -36864,7 +36861,7 @@
       </c>
       <c r="S615" s="10"/>
     </row>
-    <row r="616" spans="1:19" ht="11" customHeight="1">
+    <row r="616" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A616" s="8" t="s">
         <v>170</v>
       </c>
@@ -36921,7 +36918,7 @@
       </c>
       <c r="S616" s="10"/>
     </row>
-    <row r="617" spans="1:19" ht="11" customHeight="1">
+    <row r="617" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A617" s="8" t="s">
         <v>170</v>
       </c>
@@ -36978,7 +36975,7 @@
       </c>
       <c r="S617" s="10"/>
     </row>
-    <row r="618" spans="1:19" ht="11" customHeight="1">
+    <row r="618" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A618" s="8" t="s">
         <v>170</v>
       </c>
@@ -37037,7 +37034,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="619" spans="1:19" ht="11" customHeight="1">
+    <row r="619" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A619" s="8" t="s">
         <v>170</v>
       </c>
@@ -37096,7 +37093,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="620" spans="1:19" ht="11" customHeight="1">
+    <row r="620" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A620" s="8" t="s">
         <v>170</v>
       </c>
@@ -37153,7 +37150,7 @@
       </c>
       <c r="S620" s="10"/>
     </row>
-    <row r="621" spans="1:19" ht="11" customHeight="1">
+    <row r="621" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A621" s="8" t="s">
         <v>170</v>
       </c>
@@ -37210,7 +37207,7 @@
       </c>
       <c r="S621" s="10"/>
     </row>
-    <row r="622" spans="1:19" ht="11" customHeight="1">
+    <row r="622" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A622" s="8" t="s">
         <v>170</v>
       </c>
@@ -37267,7 +37264,7 @@
       </c>
       <c r="S622" s="10"/>
     </row>
-    <row r="623" spans="1:19" ht="11" customHeight="1">
+    <row r="623" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A623" s="8" t="s">
         <v>170</v>
       </c>
@@ -37326,7 +37323,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="624" spans="1:19" ht="11" customHeight="1">
+    <row r="624" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A624" s="8" t="s">
         <v>170</v>
       </c>
@@ -37379,7 +37376,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="625" spans="1:19" ht="11" customHeight="1">
+    <row r="625" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A625" s="8" t="s">
         <v>170</v>
       </c>
@@ -37432,7 +37429,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="626" spans="1:19" ht="11" customHeight="1">
+    <row r="626" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A626" s="8" t="s">
         <v>170</v>
       </c>
@@ -37485,7 +37482,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="627" spans="1:19" ht="11" customHeight="1">
+    <row r="627" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A627" s="8" t="s">
         <v>170</v>
       </c>
@@ -37544,7 +37541,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="628" spans="1:19" ht="11" customHeight="1">
+    <row r="628" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A628" s="8" t="s">
         <v>170</v>
       </c>
@@ -37603,7 +37600,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="629" spans="1:19" ht="11" customHeight="1">
+    <row r="629" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A629" s="8" t="s">
         <v>170</v>
       </c>
@@ -37660,7 +37657,7 @@
       </c>
       <c r="S629" s="10"/>
     </row>
-    <row r="630" spans="1:19" ht="11" customHeight="1">
+    <row r="630" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A630" s="8" t="s">
         <v>170</v>
       </c>
@@ -37717,7 +37714,7 @@
       </c>
       <c r="S630" s="10"/>
     </row>
-    <row r="631" spans="1:19" ht="11" customHeight="1">
+    <row r="631" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A631" s="8" t="s">
         <v>170</v>
       </c>
@@ -37774,7 +37771,7 @@
       </c>
       <c r="S631" s="10"/>
     </row>
-    <row r="632" spans="1:19" ht="11" customHeight="1">
+    <row r="632" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A632" s="8" t="s">
         <v>170</v>
       </c>
@@ -37833,7 +37830,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="633" spans="1:19" ht="11" customHeight="1">
+    <row r="633" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A633" s="8" t="s">
         <v>170</v>
       </c>
@@ -37886,7 +37883,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="634" spans="1:19" ht="11" customHeight="1">
+    <row r="634" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A634" s="8" t="s">
         <v>170</v>
       </c>
@@ -37945,7 +37942,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="635" spans="1:19" ht="11" customHeight="1">
+    <row r="635" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A635" s="8" t="s">
         <v>170</v>
       </c>
@@ -38002,7 +37999,7 @@
       </c>
       <c r="S635" s="10"/>
     </row>
-    <row r="636" spans="1:19" ht="11" customHeight="1">
+    <row r="636" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A636" s="8" t="s">
         <v>170</v>
       </c>
@@ -38059,7 +38056,7 @@
       </c>
       <c r="S636" s="10"/>
     </row>
-    <row r="637" spans="1:19" ht="11" customHeight="1">
+    <row r="637" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A637" s="8" t="s">
         <v>170</v>
       </c>
@@ -38118,7 +38115,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="638" spans="1:19" ht="11" customHeight="1">
+    <row r="638" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A638" s="8" t="s">
         <v>170</v>
       </c>
@@ -38175,7 +38172,7 @@
       </c>
       <c r="S638" s="10"/>
     </row>
-    <row r="639" spans="1:19" ht="11" customHeight="1">
+    <row r="639" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A639" s="8" t="s">
         <v>170</v>
       </c>
@@ -38228,7 +38225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="640" spans="1:19" ht="11" customHeight="1">
+    <row r="640" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A640" s="8" t="s">
         <v>170</v>
       </c>
@@ -38285,7 +38282,7 @@
       </c>
       <c r="S640" s="10"/>
     </row>
-    <row r="641" spans="1:19" ht="11" customHeight="1">
+    <row r="641" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A641" s="8" t="s">
         <v>170</v>
       </c>
@@ -38338,7 +38335,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="642" spans="1:19" ht="11" customHeight="1">
+    <row r="642" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A642" s="8" t="s">
         <v>170</v>
       </c>
@@ -38395,7 +38392,7 @@
       </c>
       <c r="S642" s="10"/>
     </row>
-    <row r="643" spans="1:19" ht="11" customHeight="1">
+    <row r="643" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A643" s="8" t="s">
         <v>170</v>
       </c>
@@ -38448,7 +38445,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="644" spans="1:19" ht="11" customHeight="1">
+    <row r="644" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A644" s="8" t="s">
         <v>170</v>
       </c>
@@ -38501,7 +38498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="645" spans="1:19" ht="11" customHeight="1">
+    <row r="645" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A645" s="8" t="s">
         <v>170</v>
       </c>
@@ -38558,7 +38555,7 @@
       </c>
       <c r="S645" s="10"/>
     </row>
-    <row r="646" spans="1:19" ht="11" customHeight="1">
+    <row r="646" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A646" s="8" t="s">
         <v>170</v>
       </c>
@@ -38617,7 +38614,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="647" spans="1:19" ht="11" customHeight="1">
+    <row r="647" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A647" s="8" t="s">
         <v>170</v>
       </c>
@@ -38676,7 +38673,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="648" spans="1:19" ht="11" customHeight="1">
+    <row r="648" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A648" s="8" t="s">
         <v>170</v>
       </c>
@@ -38733,7 +38730,7 @@
       </c>
       <c r="S648" s="10"/>
     </row>
-    <row r="649" spans="1:19" ht="11" customHeight="1">
+    <row r="649" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A649" s="8" t="s">
         <v>170</v>
       </c>
@@ -38790,7 +38787,7 @@
       </c>
       <c r="S649" s="10"/>
     </row>
-    <row r="650" spans="1:19" ht="11" customHeight="1">
+    <row r="650" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A650" s="8" t="s">
         <v>170</v>
       </c>
@@ -38843,7 +38840,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="651" spans="1:19" ht="11" customHeight="1">
+    <row r="651" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A651" s="8" t="s">
         <v>170</v>
       </c>
@@ -38896,7 +38893,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="652" spans="1:19" ht="11" customHeight="1">
+    <row r="652" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A652" s="8" t="s">
         <v>170</v>
       </c>
@@ -38949,7 +38946,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="653" spans="1:19" ht="11" customHeight="1">
+    <row r="653" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A653" s="8" t="s">
         <v>170</v>
       </c>
@@ -39008,7 +39005,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="654" spans="1:19" ht="11" customHeight="1">
+    <row r="654" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A654" s="8" t="s">
         <v>170</v>
       </c>
@@ -39065,7 +39062,7 @@
       </c>
       <c r="S654" s="10"/>
     </row>
-    <row r="655" spans="1:19" ht="11" customHeight="1">
+    <row r="655" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A655" s="8" t="s">
         <v>170</v>
       </c>
@@ -39124,7 +39121,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="656" spans="1:19" ht="11" customHeight="1">
+    <row r="656" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A656" s="8" t="s">
         <v>170</v>
       </c>
@@ -39181,7 +39178,7 @@
       </c>
       <c r="S656" s="10"/>
     </row>
-    <row r="657" spans="1:19" ht="11" customHeight="1">
+    <row r="657" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A657" s="8" t="s">
         <v>170</v>
       </c>
@@ -39238,7 +39235,7 @@
       </c>
       <c r="S657" s="10"/>
     </row>
-    <row r="658" spans="1:19" ht="11" customHeight="1">
+    <row r="658" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A658" s="8" t="s">
         <v>170</v>
       </c>
@@ -39295,7 +39292,7 @@
       </c>
       <c r="S658" s="10"/>
     </row>
-    <row r="659" spans="1:19" ht="11" customHeight="1">
+    <row r="659" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A659" s="8" t="s">
         <v>170</v>
       </c>
@@ -39352,7 +39349,7 @@
       </c>
       <c r="S659" s="10"/>
     </row>
-    <row r="660" spans="1:19" ht="11" customHeight="1">
+    <row r="660" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A660" s="8" t="s">
         <v>170</v>
       </c>
@@ -39409,7 +39406,7 @@
       </c>
       <c r="S660" s="10"/>
     </row>
-    <row r="661" spans="1:19" ht="11" customHeight="1">
+    <row r="661" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A661" s="8" t="s">
         <v>170</v>
       </c>
@@ -39466,7 +39463,7 @@
       </c>
       <c r="S661" s="10"/>
     </row>
-    <row r="662" spans="1:19" ht="11" customHeight="1">
+    <row r="662" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A662" s="8" t="s">
         <v>170</v>
       </c>
@@ -39523,7 +39520,7 @@
       </c>
       <c r="S662" s="10"/>
     </row>
-    <row r="663" spans="1:19" ht="11" customHeight="1">
+    <row r="663" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A663" s="8" t="s">
         <v>170</v>
       </c>
@@ -39580,7 +39577,7 @@
       </c>
       <c r="S663" s="10"/>
     </row>
-    <row r="664" spans="1:19" ht="11" customHeight="1">
+    <row r="664" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A664" s="8" t="s">
         <v>170</v>
       </c>
@@ -39637,7 +39634,7 @@
       </c>
       <c r="S664" s="10"/>
     </row>
-    <row r="665" spans="1:19" ht="11" customHeight="1">
+    <row r="665" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A665" s="8" t="s">
         <v>170</v>
       </c>
@@ -39694,7 +39691,7 @@
       </c>
       <c r="S665" s="10"/>
     </row>
-    <row r="666" spans="1:19" ht="11" customHeight="1">
+    <row r="666" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A666" s="8" t="s">
         <v>170</v>
       </c>
@@ -39751,7 +39748,7 @@
       </c>
       <c r="S666" s="10"/>
     </row>
-    <row r="667" spans="1:19" ht="11" customHeight="1">
+    <row r="667" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A667" s="8" t="s">
         <v>170</v>
       </c>
@@ -39808,7 +39805,7 @@
       </c>
       <c r="S667" s="10"/>
     </row>
-    <row r="668" spans="1:19" ht="11" customHeight="1">
+    <row r="668" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A668" s="8" t="s">
         <v>170</v>
       </c>
@@ -39865,7 +39862,7 @@
       </c>
       <c r="S668" s="10"/>
     </row>
-    <row r="669" spans="1:19" ht="11" customHeight="1">
+    <row r="669" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A669" s="8" t="s">
         <v>170</v>
       </c>
@@ -39922,7 +39919,7 @@
       </c>
       <c r="S669" s="10"/>
     </row>
-    <row r="670" spans="1:19" ht="11" customHeight="1">
+    <row r="670" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A670" s="8" t="s">
         <v>170</v>
       </c>
@@ -39981,7 +39978,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="671" spans="1:19" ht="11" customHeight="1">
+    <row r="671" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A671" s="8" t="s">
         <v>170</v>
       </c>
@@ -40038,7 +40035,7 @@
       </c>
       <c r="S671" s="10"/>
     </row>
-    <row r="672" spans="1:19" ht="11" customHeight="1">
+    <row r="672" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A672" s="8" t="s">
         <v>170</v>
       </c>
@@ -40095,7 +40092,7 @@
       </c>
       <c r="S672" s="10"/>
     </row>
-    <row r="673" spans="1:19" ht="11" customHeight="1">
+    <row r="673" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A673" s="8" t="s">
         <v>170</v>
       </c>
@@ -40154,7 +40151,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="674" spans="1:19" ht="11" customHeight="1">
+    <row r="674" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A674" s="8" t="s">
         <v>170</v>
       </c>
@@ -40213,7 +40210,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="675" spans="1:19" ht="11" customHeight="1">
+    <row r="675" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A675" s="8" t="s">
         <v>170</v>
       </c>
@@ -40270,7 +40267,7 @@
       </c>
       <c r="S675" s="10"/>
     </row>
-    <row r="676" spans="1:19" ht="11" customHeight="1">
+    <row r="676" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A676" s="8" t="s">
         <v>170</v>
       </c>
@@ -40329,7 +40326,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="677" spans="1:19" ht="11" customHeight="1">
+    <row r="677" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A677" s="8" t="s">
         <v>170</v>
       </c>
@@ -40386,7 +40383,7 @@
       </c>
       <c r="S677" s="10"/>
     </row>
-    <row r="678" spans="1:19" ht="11" customHeight="1">
+    <row r="678" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A678" s="8" t="s">
         <v>170</v>
       </c>
@@ -40443,7 +40440,7 @@
       </c>
       <c r="S678" s="10"/>
     </row>
-    <row r="679" spans="1:19" ht="11" customHeight="1">
+    <row r="679" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A679" s="8" t="s">
         <v>170</v>
       </c>
@@ -40500,7 +40497,7 @@
       </c>
       <c r="S679" s="10"/>
     </row>
-    <row r="680" spans="1:19" ht="11" customHeight="1">
+    <row r="680" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A680" s="8" t="s">
         <v>170</v>
       </c>
@@ -40557,7 +40554,7 @@
       </c>
       <c r="S680" s="10"/>
     </row>
-    <row r="681" spans="1:19" ht="11" customHeight="1">
+    <row r="681" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A681" s="8" t="s">
         <v>170</v>
       </c>
@@ -40616,7 +40613,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="682" spans="1:19" ht="11" customHeight="1">
+    <row r="682" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A682" s="8" t="s">
         <v>170</v>
       </c>
@@ -40673,7 +40670,7 @@
       </c>
       <c r="S682" s="10"/>
     </row>
-    <row r="683" spans="1:19" ht="11" customHeight="1">
+    <row r="683" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A683" s="8" t="s">
         <v>170</v>
       </c>
@@ -40732,7 +40729,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="684" spans="1:19" ht="11" customHeight="1">
+    <row r="684" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A684" s="8" t="s">
         <v>170</v>
       </c>
@@ -40789,7 +40786,7 @@
       </c>
       <c r="S684" s="10"/>
     </row>
-    <row r="685" spans="1:19" ht="11" customHeight="1">
+    <row r="685" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A685" s="8" t="s">
         <v>170</v>
       </c>
@@ -40846,7 +40843,7 @@
       </c>
       <c r="S685" s="10"/>
     </row>
-    <row r="686" spans="1:19" ht="11" customHeight="1">
+    <row r="686" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A686" s="8" t="s">
         <v>170</v>
       </c>
@@ -40903,7 +40900,7 @@
       </c>
       <c r="S686" s="10"/>
     </row>
-    <row r="687" spans="1:19" ht="11" customHeight="1">
+    <row r="687" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A687" s="8" t="s">
         <v>170</v>
       </c>
@@ -40962,7 +40959,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="688" spans="1:19" ht="11" customHeight="1">
+    <row r="688" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A688" s="8" t="s">
         <v>170</v>
       </c>
@@ -41019,7 +41016,7 @@
       </c>
       <c r="S688" s="10"/>
     </row>
-    <row r="689" spans="1:19" ht="11" customHeight="1">
+    <row r="689" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A689" s="8" t="s">
         <v>170</v>
       </c>
@@ -41076,7 +41073,7 @@
       </c>
       <c r="S689" s="10"/>
     </row>
-    <row r="690" spans="1:19" ht="11" customHeight="1">
+    <row r="690" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A690" s="8" t="s">
         <v>170</v>
       </c>
@@ -41129,7 +41126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="691" spans="1:19" ht="11" customHeight="1">
+    <row r="691" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A691" s="8" t="s">
         <v>170</v>
       </c>
@@ -41182,7 +41179,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="692" spans="1:19" ht="11" customHeight="1">
+    <row r="692" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A692" s="8" t="s">
         <v>170</v>
       </c>
@@ -41235,7 +41232,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="693" spans="1:19" ht="11" customHeight="1">
+    <row r="693" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A693" s="8" t="s">
         <v>170</v>
       </c>
@@ -41294,7 +41291,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="694" spans="1:19" ht="11" customHeight="1">
+    <row r="694" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A694" s="8" t="s">
         <v>170</v>
       </c>
@@ -41351,7 +41348,7 @@
       </c>
       <c r="S694" s="10"/>
     </row>
-    <row r="695" spans="1:19" ht="11" customHeight="1">
+    <row r="695" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A695" s="8" t="s">
         <v>170</v>
       </c>
@@ -41408,7 +41405,7 @@
       </c>
       <c r="S695" s="10"/>
     </row>
-    <row r="696" spans="1:19" ht="11" customHeight="1">
+    <row r="696" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A696" s="8" t="s">
         <v>170</v>
       </c>
@@ -41467,7 +41464,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="697" spans="1:19" ht="11" customHeight="1">
+    <row r="697" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A697" s="8" t="s">
         <v>170</v>
       </c>
@@ -41526,7 +41523,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="698" spans="1:19" ht="11" customHeight="1">
+    <row r="698" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A698" s="8" t="s">
         <v>170</v>
       </c>
@@ -41583,7 +41580,7 @@
       </c>
       <c r="S698" s="10"/>
     </row>
-    <row r="699" spans="1:19" ht="11" customHeight="1">
+    <row r="699" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A699" s="8" t="s">
         <v>170</v>
       </c>
@@ -41642,7 +41639,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="700" spans="1:19" ht="11" customHeight="1">
+    <row r="700" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A700" s="8" t="s">
         <v>170</v>
       </c>
@@ -41701,7 +41698,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="701" spans="1:19" ht="11" customHeight="1">
+    <row r="701" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A701" s="8" t="s">
         <v>170</v>
       </c>
@@ -41758,7 +41755,7 @@
       </c>
       <c r="S701" s="10"/>
     </row>
-    <row r="702" spans="1:19" ht="11" customHeight="1">
+    <row r="702" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A702" s="8" t="s">
         <v>170</v>
       </c>
@@ -41817,7 +41814,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="703" spans="1:19" ht="11" customHeight="1">
+    <row r="703" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A703" s="8" t="s">
         <v>170</v>
       </c>
@@ -41874,7 +41871,7 @@
       </c>
       <c r="S703" s="10"/>
     </row>
-    <row r="704" spans="1:19" ht="11" customHeight="1">
+    <row r="704" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A704" s="8" t="s">
         <v>170</v>
       </c>
@@ -41931,7 +41928,7 @@
       </c>
       <c r="S704" s="10"/>
     </row>
-    <row r="705" spans="1:19" ht="11" customHeight="1">
+    <row r="705" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A705" s="8" t="s">
         <v>170</v>
       </c>
@@ -41988,7 +41985,7 @@
       </c>
       <c r="S705" s="10"/>
     </row>
-    <row r="706" spans="1:19" ht="11" customHeight="1">
+    <row r="706" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A706" s="8" t="s">
         <v>170</v>
       </c>
@@ -42045,7 +42042,7 @@
       </c>
       <c r="S706" s="10"/>
     </row>
-    <row r="707" spans="1:19" ht="11" customHeight="1">
+    <row r="707" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A707" s="8" t="s">
         <v>170</v>
       </c>
@@ -42104,7 +42101,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="708" spans="1:19" ht="11" customHeight="1">
+    <row r="708" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A708" s="8" t="s">
         <v>170</v>
       </c>
@@ -42163,7 +42160,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="709" spans="1:19" ht="11" customHeight="1">
+    <row r="709" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A709" s="8" t="s">
         <v>170</v>
       </c>
@@ -42220,7 +42217,7 @@
       </c>
       <c r="S709" s="10"/>
     </row>
-    <row r="710" spans="1:19" ht="11" customHeight="1">
+    <row r="710" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A710" s="8" t="s">
         <v>170</v>
       </c>
@@ -42277,7 +42274,7 @@
       </c>
       <c r="S710" s="10"/>
     </row>
-    <row r="711" spans="1:19" ht="11" customHeight="1">
+    <row r="711" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A711" s="8" t="s">
         <v>170</v>
       </c>
@@ -42334,7 +42331,7 @@
       </c>
       <c r="S711" s="10"/>
     </row>
-    <row r="712" spans="1:19" ht="11" customHeight="1">
+    <row r="712" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A712" s="8" t="s">
         <v>170</v>
       </c>
@@ -42391,7 +42388,7 @@
       </c>
       <c r="S712" s="10"/>
     </row>
-    <row r="713" spans="1:19" ht="11" customHeight="1">
+    <row r="713" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A713" s="8" t="s">
         <v>170</v>
       </c>
@@ -42448,7 +42445,7 @@
       </c>
       <c r="S713" s="10"/>
     </row>
-    <row r="714" spans="1:19" ht="11" customHeight="1">
+    <row r="714" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A714" s="8" t="s">
         <v>170</v>
       </c>
@@ -42507,7 +42504,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="715" spans="1:19" ht="11" customHeight="1">
+    <row r="715" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A715" s="8" t="s">
         <v>170</v>
       </c>
@@ -42564,7 +42561,7 @@
       </c>
       <c r="S715" s="10"/>
     </row>
-    <row r="716" spans="1:19" ht="11" customHeight="1">
+    <row r="716" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A716" s="8" t="s">
         <v>170</v>
       </c>
@@ -42621,7 +42618,7 @@
       </c>
       <c r="S716" s="10"/>
     </row>
-    <row r="717" spans="1:19" ht="11" customHeight="1">
+    <row r="717" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A717" s="8" t="s">
         <v>170</v>
       </c>
@@ -42680,7 +42677,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="718" spans="1:19" ht="11" customHeight="1">
+    <row r="718" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A718" s="8" t="s">
         <v>170</v>
       </c>
@@ -42737,7 +42734,7 @@
       </c>
       <c r="S718" s="10"/>
     </row>
-    <row r="719" spans="1:19" ht="11" customHeight="1">
+    <row r="719" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A719" s="8" t="s">
         <v>170</v>
       </c>
@@ -42794,7 +42791,7 @@
       </c>
       <c r="S719" s="10"/>
     </row>
-    <row r="720" spans="1:19" ht="11" customHeight="1">
+    <row r="720" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A720" s="8" t="s">
         <v>170</v>
       </c>
@@ -42853,7 +42850,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="721" spans="1:19" ht="11" customHeight="1">
+    <row r="721" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A721" s="8" t="s">
         <v>170</v>
       </c>
@@ -42910,7 +42907,7 @@
       </c>
       <c r="S721" s="10"/>
     </row>
-    <row r="722" spans="1:19" ht="11" customHeight="1">
+    <row r="722" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A722" s="8" t="s">
         <v>170</v>
       </c>
@@ -42967,7 +42964,7 @@
       </c>
       <c r="S722" s="10"/>
     </row>
-    <row r="723" spans="1:19" ht="11" customHeight="1">
+    <row r="723" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A723" s="8" t="s">
         <v>170</v>
       </c>
@@ -43024,7 +43021,7 @@
       </c>
       <c r="S723" s="10"/>
     </row>
-    <row r="724" spans="1:19" ht="11" customHeight="1">
+    <row r="724" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A724" s="8" t="s">
         <v>170</v>
       </c>
@@ -43083,7 +43080,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="725" spans="1:19" ht="11" customHeight="1">
+    <row r="725" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A725" s="8" t="s">
         <v>170</v>
       </c>
@@ -43140,7 +43137,7 @@
       </c>
       <c r="S725" s="10"/>
     </row>
-    <row r="726" spans="1:19" ht="11" customHeight="1">
+    <row r="726" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A726" s="8" t="s">
         <v>170</v>
       </c>
@@ -43197,7 +43194,7 @@
       </c>
       <c r="S726" s="10"/>
     </row>
-    <row r="727" spans="1:19" ht="11" customHeight="1">
+    <row r="727" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A727" s="8" t="s">
         <v>170</v>
       </c>
@@ -43254,7 +43251,7 @@
       </c>
       <c r="S727" s="10"/>
     </row>
-    <row r="728" spans="1:19" ht="11" customHeight="1">
+    <row r="728" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A728" s="8" t="s">
         <v>170</v>
       </c>
@@ -43311,7 +43308,7 @@
       </c>
       <c r="S728" s="10"/>
     </row>
-    <row r="729" spans="1:19" ht="11" customHeight="1">
+    <row r="729" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A729" s="8" t="s">
         <v>170</v>
       </c>
@@ -43368,7 +43365,7 @@
       </c>
       <c r="S729" s="10"/>
     </row>
-    <row r="730" spans="1:19" ht="11" customHeight="1">
+    <row r="730" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A730" s="8" t="s">
         <v>170</v>
       </c>
@@ -43425,7 +43422,7 @@
       </c>
       <c r="S730" s="10"/>
     </row>
-    <row r="731" spans="1:19" ht="11" customHeight="1">
+    <row r="731" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A731" s="8" t="s">
         <v>170</v>
       </c>
@@ -43482,7 +43479,7 @@
       </c>
       <c r="S731" s="10"/>
     </row>
-    <row r="732" spans="1:19" ht="11" customHeight="1">
+    <row r="732" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A732" s="8" t="s">
         <v>170</v>
       </c>
@@ -43539,7 +43536,7 @@
       </c>
       <c r="S732" s="10"/>
     </row>
-    <row r="733" spans="1:19" ht="11" customHeight="1">
+    <row r="733" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A733" s="8" t="s">
         <v>170</v>
       </c>
@@ -43598,7 +43595,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="734" spans="1:19" ht="11" customHeight="1">
+    <row r="734" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A734" s="8" t="s">
         <v>170</v>
       </c>
@@ -43655,7 +43652,7 @@
       </c>
       <c r="S734" s="10"/>
     </row>
-    <row r="735" spans="1:19" ht="11" customHeight="1">
+    <row r="735" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A735" s="8" t="s">
         <v>170</v>
       </c>
@@ -43712,7 +43709,7 @@
       </c>
       <c r="S735" s="10"/>
     </row>
-    <row r="736" spans="1:19" ht="11" customHeight="1">
+    <row r="736" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A736" s="8" t="s">
         <v>170</v>
       </c>
@@ -43771,7 +43768,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="737" spans="1:19" ht="11" customHeight="1">
+    <row r="737" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A737" s="8" t="s">
         <v>191</v>
       </c>
@@ -43830,7 +43827,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="738" spans="1:19" ht="11" customHeight="1">
+    <row r="738" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A738" s="8" t="s">
         <v>191</v>
       </c>
@@ -43883,7 +43880,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="739" spans="1:19" ht="11" customHeight="1">
+    <row r="739" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A739" s="8" t="s">
         <v>191</v>
       </c>
@@ -43942,7 +43939,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="740" spans="1:19" ht="11" customHeight="1">
+    <row r="740" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A740" s="8" t="s">
         <v>191</v>
       </c>
@@ -43993,7 +43990,7 @@
       </c>
       <c r="S740" s="10"/>
     </row>
-    <row r="741" spans="1:19" ht="11" customHeight="1">
+    <row r="741" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A741" s="8" t="s">
         <v>191</v>
       </c>
@@ -44052,7 +44049,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="742" spans="1:19" ht="11" customHeight="1">
+    <row r="742" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A742" s="8" t="s">
         <v>191</v>
       </c>
@@ -44105,7 +44102,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="743" spans="1:19" ht="11" customHeight="1">
+    <row r="743" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A743" s="8" t="s">
         <v>191</v>
       </c>
@@ -44158,7 +44155,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="744" spans="1:19" ht="11" customHeight="1">
+    <row r="744" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A744" s="8" t="s">
         <v>191</v>
       </c>
@@ -44217,7 +44214,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="745" spans="1:19" ht="11" customHeight="1">
+    <row r="745" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A745" s="8" t="s">
         <v>191</v>
       </c>
@@ -44276,7 +44273,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="746" spans="1:19" ht="11" customHeight="1">
+    <row r="746" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A746" s="8" t="s">
         <v>191</v>
       </c>
@@ -44333,7 +44330,7 @@
       </c>
       <c r="S746" s="10"/>
     </row>
-    <row r="747" spans="1:19" ht="11" customHeight="1">
+    <row r="747" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A747" s="8" t="s">
         <v>191</v>
       </c>
@@ -44390,7 +44387,7 @@
       </c>
       <c r="S747" s="10"/>
     </row>
-    <row r="748" spans="1:19" ht="11" customHeight="1">
+    <row r="748" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A748" s="8" t="s">
         <v>191</v>
       </c>
@@ -44447,7 +44444,7 @@
       </c>
       <c r="S748" s="10"/>
     </row>
-    <row r="749" spans="1:19" ht="11" customHeight="1">
+    <row r="749" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A749" s="8" t="s">
         <v>191</v>
       </c>
@@ -44506,7 +44503,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="750" spans="1:19" ht="11" customHeight="1">
+    <row r="750" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A750" s="8" t="s">
         <v>191</v>
       </c>
@@ -44563,7 +44560,7 @@
       </c>
       <c r="S750" s="21"/>
     </row>
-    <row r="751" spans="1:19" ht="11" customHeight="1">
+    <row r="751" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A751" s="8" t="s">
         <v>191</v>
       </c>
@@ -44620,7 +44617,7 @@
       </c>
       <c r="S751" s="10"/>
     </row>
-    <row r="752" spans="1:19" ht="11" customHeight="1">
+    <row r="752" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A752" s="8" t="s">
         <v>191</v>
       </c>
@@ -44679,7 +44676,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="753" spans="1:19" ht="11" customHeight="1">
+    <row r="753" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A753" s="8" t="s">
         <v>191</v>
       </c>
@@ -44738,7 +44735,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="754" spans="1:19" ht="11" customHeight="1">
+    <row r="754" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A754" s="8" t="s">
         <v>191</v>
       </c>
@@ -44797,7 +44794,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="755" spans="1:19" ht="11" customHeight="1">
+    <row r="755" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A755" s="8" t="s">
         <v>191</v>
       </c>
@@ -44856,7 +44853,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="756" spans="1:19" ht="11" customHeight="1">
+    <row r="756" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A756" s="8" t="s">
         <v>191</v>
       </c>
@@ -44913,7 +44910,7 @@
       </c>
       <c r="S756" s="10"/>
     </row>
-    <row r="757" spans="1:19" ht="11" customHeight="1">
+    <row r="757" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A757" s="8" t="s">
         <v>191</v>
       </c>
@@ -44966,7 +44963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="758" spans="1:19" ht="11" customHeight="1">
+    <row r="758" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A758" s="8" t="s">
         <v>191</v>
       </c>
@@ -45025,7 +45022,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="759" spans="1:19" ht="11" customHeight="1">
+    <row r="759" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A759" s="8" t="s">
         <v>191</v>
       </c>
@@ -45084,7 +45081,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="760" spans="1:19" ht="11" customHeight="1">
+    <row r="760" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A760" s="8" t="s">
         <v>191</v>
       </c>
@@ -45143,7 +45140,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="761" spans="1:19" ht="11" customHeight="1">
+    <row r="761" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A761" s="8" t="s">
         <v>191</v>
       </c>
@@ -45202,7 +45199,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="762" spans="1:19" ht="11" customHeight="1">
+    <row r="762" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A762" s="8" t="s">
         <v>191</v>
       </c>
@@ -45255,7 +45252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="763" spans="1:19" ht="11" customHeight="1">
+    <row r="763" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A763" s="8" t="s">
         <v>191</v>
       </c>
@@ -45312,7 +45309,7 @@
       </c>
       <c r="S763" s="10"/>
     </row>
-    <row r="764" spans="1:19" ht="11" customHeight="1">
+    <row r="764" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A764" s="8" t="s">
         <v>191</v>
       </c>
@@ -45369,7 +45366,7 @@
       </c>
       <c r="S764" s="10"/>
     </row>
-    <row r="765" spans="1:19" ht="11" customHeight="1">
+    <row r="765" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A765" s="8" t="s">
         <v>191</v>
       </c>
@@ -45428,7 +45425,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="766" spans="1:19" ht="11" customHeight="1">
+    <row r="766" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A766" s="8" t="s">
         <v>191</v>
       </c>
@@ -45485,7 +45482,7 @@
       </c>
       <c r="S766" s="10"/>
     </row>
-    <row r="767" spans="1:19" ht="11" customHeight="1">
+    <row r="767" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A767" s="8" t="s">
         <v>191</v>
       </c>
@@ -45538,7 +45535,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="768" spans="1:19" ht="11" customHeight="1">
+    <row r="768" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A768" s="8" t="s">
         <v>191</v>
       </c>
@@ -45597,7 +45594,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="769" spans="1:19" ht="11" customHeight="1">
+    <row r="769" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A769" s="8" t="s">
         <v>191</v>
       </c>
@@ -45654,7 +45651,7 @@
       </c>
       <c r="S769" s="10"/>
     </row>
-    <row r="770" spans="1:19" ht="11" customHeight="1">
+    <row r="770" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A770" s="8" t="s">
         <v>191</v>
       </c>
@@ -45711,7 +45708,7 @@
       </c>
       <c r="S770" s="10"/>
     </row>
-    <row r="771" spans="1:19" ht="11" customHeight="1">
+    <row r="771" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A771" s="8" t="s">
         <v>191</v>
       </c>
@@ -45770,7 +45767,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="772" spans="1:19" ht="11" customHeight="1">
+    <row r="772" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A772" s="8" t="s">
         <v>191</v>
       </c>
@@ -45829,7 +45826,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="773" spans="1:19" ht="11" customHeight="1">
+    <row r="773" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A773" s="8" t="s">
         <v>191</v>
       </c>
@@ -45886,7 +45883,7 @@
       </c>
       <c r="S773" s="10"/>
     </row>
-    <row r="774" spans="1:19" ht="11" customHeight="1">
+    <row r="774" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A774" s="8" t="s">
         <v>191</v>
       </c>
@@ -45939,7 +45936,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="775" spans="1:19" ht="11" customHeight="1">
+    <row r="775" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A775" s="8" t="s">
         <v>191</v>
       </c>
@@ -45992,7 +45989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="776" spans="1:19" ht="11" customHeight="1">
+    <row r="776" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A776" s="8" t="s">
         <v>191</v>
       </c>
@@ -46051,7 +46048,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="777" spans="1:19" ht="11" customHeight="1">
+    <row r="777" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A777" s="8" t="s">
         <v>191</v>
       </c>
@@ -46110,7 +46107,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="778" spans="1:19" ht="11" customHeight="1">
+    <row r="778" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A778" s="8" t="s">
         <v>191</v>
       </c>
@@ -46167,7 +46164,7 @@
       </c>
       <c r="S778" s="10"/>
     </row>
-    <row r="779" spans="1:19" ht="11" customHeight="1">
+    <row r="779" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A779" s="8" t="s">
         <v>191</v>
       </c>
@@ -46220,7 +46217,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="780" spans="1:19" ht="11" customHeight="1">
+    <row r="780" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A780" s="8" t="s">
         <v>191</v>
       </c>
@@ -46277,7 +46274,7 @@
       </c>
       <c r="S780" s="10"/>
     </row>
-    <row r="781" spans="1:19" ht="11" customHeight="1">
+    <row r="781" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A781" s="8" t="s">
         <v>191</v>
       </c>
@@ -46334,7 +46331,7 @@
       </c>
       <c r="S781" s="10"/>
     </row>
-    <row r="782" spans="1:19" ht="11" customHeight="1">
+    <row r="782" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A782" s="8" t="s">
         <v>191</v>
       </c>
@@ -46391,7 +46388,7 @@
       </c>
       <c r="S782" s="10"/>
     </row>
-    <row r="783" spans="1:19" ht="11" customHeight="1">
+    <row r="783" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A783" s="8" t="s">
         <v>191</v>
       </c>
@@ -46450,7 +46447,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="784" spans="1:19" ht="11" customHeight="1">
+    <row r="784" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A784" s="8" t="s">
         <v>191</v>
       </c>
@@ -46503,7 +46500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="785" spans="1:19" ht="11" customHeight="1">
+    <row r="785" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A785" s="8" t="s">
         <v>191</v>
       </c>
@@ -46560,7 +46557,7 @@
       </c>
       <c r="S785" s="10"/>
     </row>
-    <row r="786" spans="1:19" ht="11" customHeight="1">
+    <row r="786" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A786" s="8" t="s">
         <v>191</v>
       </c>
@@ -46617,7 +46614,7 @@
       </c>
       <c r="S786" s="10"/>
     </row>
-    <row r="787" spans="1:19" ht="11" customHeight="1">
+    <row r="787" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A787" s="8" t="s">
         <v>191</v>
       </c>
@@ -46674,7 +46671,7 @@
       </c>
       <c r="S787" s="10"/>
     </row>
-    <row r="788" spans="1:19" ht="11" customHeight="1">
+    <row r="788" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A788" s="8" t="s">
         <v>191</v>
       </c>
@@ -46727,7 +46724,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="789" spans="1:19" ht="11" customHeight="1">
+    <row r="789" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A789" s="8" t="s">
         <v>191</v>
       </c>
@@ -46784,7 +46781,7 @@
       </c>
       <c r="S789" s="10"/>
     </row>
-    <row r="790" spans="1:19" ht="11" customHeight="1">
+    <row r="790" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A790" s="8" t="s">
         <v>191</v>
       </c>
@@ -46843,7 +46840,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="791" spans="1:19" ht="11" customHeight="1">
+    <row r="791" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A791" s="8" t="s">
         <v>191</v>
       </c>
@@ -46900,7 +46897,7 @@
       </c>
       <c r="S791" s="10"/>
     </row>
-    <row r="792" spans="1:19" ht="11" customHeight="1">
+    <row r="792" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A792" s="8" t="s">
         <v>191</v>
       </c>
@@ -46957,7 +46954,7 @@
       </c>
       <c r="S792" s="10"/>
     </row>
-    <row r="793" spans="1:19" ht="11" customHeight="1">
+    <row r="793" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A793" s="8" t="s">
         <v>191</v>
       </c>
@@ -47010,7 +47007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="794" spans="1:19" ht="11" customHeight="1">
+    <row r="794" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A794" s="8" t="s">
         <v>191</v>
       </c>
@@ -47067,7 +47064,7 @@
       </c>
       <c r="S794" s="10"/>
     </row>
-    <row r="795" spans="1:19" ht="11" customHeight="1">
+    <row r="795" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A795" s="8" t="s">
         <v>191</v>
       </c>
@@ -47124,7 +47121,7 @@
       </c>
       <c r="S795" s="10"/>
     </row>
-    <row r="796" spans="1:19" ht="11" customHeight="1">
+    <row r="796" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A796" s="8" t="s">
         <v>191</v>
       </c>
@@ -47177,7 +47174,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="797" spans="1:19" ht="11" customHeight="1">
+    <row r="797" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A797" s="8" t="s">
         <v>191</v>
       </c>
@@ -47234,7 +47231,7 @@
       </c>
       <c r="S797" s="10"/>
     </row>
-    <row r="798" spans="1:19" ht="11" customHeight="1">
+    <row r="798" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A798" s="8" t="s">
         <v>191</v>
       </c>
@@ -47293,7 +47290,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="799" spans="1:19" ht="11" customHeight="1">
+    <row r="799" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A799" s="8" t="s">
         <v>191</v>
       </c>
@@ -47350,7 +47347,7 @@
       </c>
       <c r="S799" s="10"/>
     </row>
-    <row r="800" spans="1:19" ht="11" customHeight="1">
+    <row r="800" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A800" s="8" t="s">
         <v>191</v>
       </c>
@@ -47409,7 +47406,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="801" spans="1:19" ht="11" customHeight="1">
+    <row r="801" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A801" s="8" t="s">
         <v>191</v>
       </c>
@@ -47466,7 +47463,7 @@
       </c>
       <c r="S801" s="10"/>
     </row>
-    <row r="802" spans="1:19" ht="11" customHeight="1">
+    <row r="802" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A802" s="8" t="s">
         <v>191</v>
       </c>
@@ -47523,7 +47520,7 @@
       </c>
       <c r="S802" s="10"/>
     </row>
-    <row r="803" spans="1:19" ht="11" customHeight="1">
+    <row r="803" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A803" s="8" t="s">
         <v>191</v>
       </c>
@@ -47582,7 +47579,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="804" spans="1:19" ht="11" customHeight="1">
+    <row r="804" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A804" s="8" t="s">
         <v>191</v>
       </c>
@@ -47639,7 +47636,7 @@
       </c>
       <c r="S804" s="10"/>
     </row>
-    <row r="805" spans="1:19" ht="11" customHeight="1">
+    <row r="805" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A805" s="8" t="s">
         <v>191</v>
       </c>
@@ -47696,7 +47693,7 @@
       </c>
       <c r="S805" s="10"/>
     </row>
-    <row r="806" spans="1:19" ht="11" customHeight="1">
+    <row r="806" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A806" s="8" t="s">
         <v>191</v>
       </c>
@@ -47749,7 +47746,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="807" spans="1:19" ht="11" customHeight="1">
+    <row r="807" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A807" s="8" t="s">
         <v>191</v>
       </c>
@@ -47802,7 +47799,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="808" spans="1:19" ht="11" customHeight="1">
+    <row r="808" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A808" s="8" t="s">
         <v>191</v>
       </c>
@@ -47859,7 +47856,7 @@
       </c>
       <c r="S808" s="10"/>
     </row>
-    <row r="809" spans="1:19" ht="11" customHeight="1">
+    <row r="809" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A809" s="8" t="s">
         <v>191</v>
       </c>
@@ -47912,7 +47909,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="810" spans="1:19" ht="11" customHeight="1">
+    <row r="810" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A810" s="8" t="s">
         <v>191</v>
       </c>
@@ -47971,7 +47968,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="811" spans="1:19" ht="11" customHeight="1">
+    <row r="811" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A811" s="8" t="s">
         <v>191</v>
       </c>
@@ -48028,7 +48025,7 @@
       </c>
       <c r="S811" s="10"/>
     </row>
-    <row r="812" spans="1:19" ht="11" customHeight="1">
+    <row r="812" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A812" s="8" t="s">
         <v>191</v>
       </c>
@@ -48085,7 +48082,7 @@
       </c>
       <c r="S812" s="10"/>
     </row>
-    <row r="813" spans="1:19" ht="11" customHeight="1">
+    <row r="813" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A813" s="8" t="s">
         <v>191</v>
       </c>
@@ -48144,7 +48141,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="814" spans="1:19" ht="11" customHeight="1">
+    <row r="814" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A814" s="8" t="s">
         <v>191</v>
       </c>
@@ -48201,7 +48198,7 @@
       </c>
       <c r="S814" s="10"/>
     </row>
-    <row r="815" spans="1:19" ht="11" customHeight="1">
+    <row r="815" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A815" s="8" t="s">
         <v>191</v>
       </c>
@@ -48258,7 +48255,7 @@
       </c>
       <c r="S815" s="10"/>
     </row>
-    <row r="816" spans="1:19" ht="11" customHeight="1">
+    <row r="816" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A816" s="8" t="s">
         <v>191</v>
       </c>
@@ -48311,7 +48308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="817" spans="1:19" ht="11" customHeight="1">
+    <row r="817" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A817" s="8" t="s">
         <v>191</v>
       </c>
@@ -48368,7 +48365,7 @@
       </c>
       <c r="S817" s="10"/>
     </row>
-    <row r="818" spans="1:19" ht="11" customHeight="1">
+    <row r="818" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A818" s="8" t="s">
         <v>191</v>
       </c>
@@ -48425,7 +48422,7 @@
       </c>
       <c r="S818" s="10"/>
     </row>
-    <row r="819" spans="1:19" ht="11" customHeight="1">
+    <row r="819" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A819" s="8" t="s">
         <v>191</v>
       </c>
@@ -48482,7 +48479,7 @@
       </c>
       <c r="S819" s="10"/>
     </row>
-    <row r="820" spans="1:19" ht="11" customHeight="1">
+    <row r="820" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A820" s="8" t="s">
         <v>191</v>
       </c>
@@ -48541,7 +48538,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="821" spans="1:19" ht="11" customHeight="1">
+    <row r="821" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A821" s="8" t="s">
         <v>191</v>
       </c>
@@ -48598,7 +48595,7 @@
       </c>
       <c r="S821" s="10"/>
     </row>
-    <row r="822" spans="1:19" ht="11" customHeight="1">
+    <row r="822" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A822" s="8" t="s">
         <v>191</v>
       </c>
@@ -48651,7 +48648,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="823" spans="1:19" ht="11" customHeight="1">
+    <row r="823" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A823" s="8" t="s">
         <v>191</v>
       </c>
@@ -48710,7 +48707,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="824" spans="1:19" ht="11" customHeight="1">
+    <row r="824" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A824" s="8" t="s">
         <v>191</v>
       </c>
@@ -48763,7 +48760,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="825" spans="1:19" ht="11" customHeight="1">
+    <row r="825" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A825" s="8" t="s">
         <v>191</v>
       </c>
@@ -48816,7 +48813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="826" spans="1:19" ht="11" customHeight="1">
+    <row r="826" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A826" s="8" t="s">
         <v>191</v>
       </c>
@@ -48873,7 +48870,7 @@
       </c>
       <c r="S826" s="10"/>
     </row>
-    <row r="827" spans="1:19" ht="11" customHeight="1">
+    <row r="827" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A827" s="8" t="s">
         <v>191</v>
       </c>
@@ -48930,7 +48927,7 @@
       </c>
       <c r="S827" s="10"/>
     </row>
-    <row r="828" spans="1:19" ht="11" customHeight="1">
+    <row r="828" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A828" s="8" t="s">
         <v>191</v>
       </c>
@@ -48989,7 +48986,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="829" spans="1:19" ht="11" customHeight="1">
+    <row r="829" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A829" s="8" t="s">
         <v>191</v>
       </c>
@@ -49046,7 +49043,7 @@
       </c>
       <c r="S829" s="10"/>
     </row>
-    <row r="830" spans="1:19" ht="11" customHeight="1">
+    <row r="830" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A830" s="8" t="s">
         <v>191</v>
       </c>
@@ -49094,7 +49091,7 @@
       </c>
       <c r="S830" s="10"/>
     </row>
-    <row r="831" spans="1:19" ht="11" customHeight="1">
+    <row r="831" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A831" s="8" t="s">
         <v>191</v>
       </c>
@@ -49153,7 +49150,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="832" spans="1:19" ht="11" customHeight="1">
+    <row r="832" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A832" s="8" t="s">
         <v>191</v>
       </c>
@@ -49210,7 +49207,7 @@
       </c>
       <c r="S832" s="10"/>
     </row>
-    <row r="833" spans="1:19" ht="11" customHeight="1">
+    <row r="833" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A833" s="8" t="s">
         <v>191</v>
       </c>
@@ -49267,7 +49264,7 @@
       </c>
       <c r="S833" s="10"/>
     </row>
-    <row r="834" spans="1:19" ht="11" customHeight="1">
+    <row r="834" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A834" s="8" t="s">
         <v>191</v>
       </c>
@@ -49324,7 +49321,7 @@
       </c>
       <c r="S834" s="10"/>
     </row>
-    <row r="835" spans="1:19" ht="11" customHeight="1">
+    <row r="835" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A835" s="8" t="s">
         <v>191</v>
       </c>
@@ -49377,7 +49374,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="836" spans="1:19" ht="11" customHeight="1">
+    <row r="836" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A836" s="8" t="s">
         <v>191</v>
       </c>
@@ -49434,7 +49431,7 @@
       </c>
       <c r="S836" s="10"/>
     </row>
-    <row r="837" spans="1:19" ht="11" customHeight="1">
+    <row r="837" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A837" s="8" t="s">
         <v>191</v>
       </c>
@@ -49491,7 +49488,7 @@
       </c>
       <c r="S837" s="10"/>
     </row>
-    <row r="838" spans="1:19" ht="11" customHeight="1">
+    <row r="838" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A838" s="8" t="s">
         <v>191</v>
       </c>
@@ -49548,7 +49545,7 @@
       </c>
       <c r="S838" s="10"/>
     </row>
-    <row r="839" spans="1:19" ht="11" customHeight="1">
+    <row r="839" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A839" s="8" t="s">
         <v>191</v>
       </c>
@@ -49599,7 +49596,7 @@
       </c>
       <c r="S839" s="10"/>
     </row>
-    <row r="840" spans="1:19" ht="11" customHeight="1">
+    <row r="840" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A840" s="8" t="s">
         <v>191</v>
       </c>
@@ -49656,7 +49653,7 @@
       </c>
       <c r="S840" s="10"/>
     </row>
-    <row r="841" spans="1:19" ht="11" customHeight="1">
+    <row r="841" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A841" s="8" t="s">
         <v>191</v>
       </c>
@@ -49715,7 +49712,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="842" spans="1:19" ht="11" customHeight="1">
+    <row r="842" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A842" s="8" t="s">
         <v>191</v>
       </c>
@@ -49772,7 +49769,7 @@
       </c>
       <c r="S842" s="10"/>
     </row>
-    <row r="843" spans="1:19" ht="11" customHeight="1">
+    <row r="843" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A843" s="8" t="s">
         <v>191</v>
       </c>
@@ -49829,7 +49826,7 @@
       </c>
       <c r="S843" s="10"/>
     </row>
-    <row r="844" spans="1:19" ht="11" customHeight="1">
+    <row r="844" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A844" s="8" t="s">
         <v>191</v>
       </c>
@@ -49886,7 +49883,7 @@
       </c>
       <c r="S844" s="10"/>
     </row>
-    <row r="845" spans="1:19" ht="11" customHeight="1">
+    <row r="845" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A845" s="8" t="s">
         <v>191</v>
       </c>
@@ -49945,7 +49942,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="846" spans="1:19" ht="11" customHeight="1">
+    <row r="846" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A846" s="8" t="s">
         <v>191</v>
       </c>
@@ -50002,7 +49999,7 @@
       </c>
       <c r="S846" s="10"/>
     </row>
-    <row r="847" spans="1:19" ht="11" customHeight="1">
+    <row r="847" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A847" s="8" t="s">
         <v>191</v>
       </c>
@@ -50061,7 +50058,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="848" spans="1:19" ht="11" customHeight="1">
+    <row r="848" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A848" s="8" t="s">
         <v>191</v>
       </c>
@@ -50120,7 +50117,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="849" spans="1:19" ht="11" customHeight="1">
+    <row r="849" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A849" s="8" t="s">
         <v>191</v>
       </c>
@@ -50173,7 +50170,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="850" spans="1:19" ht="11" customHeight="1">
+    <row r="850" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A850" s="8" t="s">
         <v>191</v>
       </c>
@@ -50226,7 +50223,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="851" spans="1:19" ht="11" customHeight="1">
+    <row r="851" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A851" s="8" t="s">
         <v>191</v>
       </c>
@@ -50283,7 +50280,7 @@
       </c>
       <c r="S851" s="10"/>
     </row>
-    <row r="852" spans="1:19" ht="11" customHeight="1">
+    <row r="852" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A852" s="8" t="s">
         <v>191</v>
       </c>
@@ -50342,7 +50339,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="853" spans="1:19" ht="11" customHeight="1">
+    <row r="853" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A853" s="8" t="s">
         <v>191</v>
       </c>
@@ -50401,7 +50398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="854" spans="1:19" ht="11" customHeight="1">
+    <row r="854" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A854" s="8" t="s">
         <v>191</v>
       </c>
@@ -50458,7 +50455,7 @@
       </c>
       <c r="S854" s="10"/>
     </row>
-    <row r="855" spans="1:19" ht="11" customHeight="1">
+    <row r="855" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A855" s="8" t="s">
         <v>191</v>
       </c>
@@ -50517,7 +50514,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="856" spans="1:19" ht="11" customHeight="1">
+    <row r="856" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A856" s="8" t="s">
         <v>191</v>
       </c>
@@ -50574,7 +50571,7 @@
       </c>
       <c r="S856" s="10"/>
     </row>
-    <row r="857" spans="1:19" ht="11" customHeight="1">
+    <row r="857" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A857" s="8" t="s">
         <v>191</v>
       </c>
@@ -50631,7 +50628,7 @@
       </c>
       <c r="S857" s="10"/>
     </row>
-    <row r="858" spans="1:19" ht="11" customHeight="1">
+    <row r="858" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A858" s="8" t="s">
         <v>191</v>
       </c>
@@ -50684,7 +50681,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="859" spans="1:19" ht="11" customHeight="1">
+    <row r="859" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A859" s="8" t="s">
         <v>191</v>
       </c>
@@ -50741,7 +50738,7 @@
       </c>
       <c r="S859" s="10"/>
     </row>
-    <row r="860" spans="1:19" ht="11" customHeight="1">
+    <row r="860" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A860" s="8" t="s">
         <v>191</v>
       </c>
@@ -50800,7 +50797,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="861" spans="1:19" ht="11" customHeight="1">
+    <row r="861" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A861" s="8" t="s">
         <v>191</v>
       </c>
@@ -50857,7 +50854,7 @@
       </c>
       <c r="S861" s="10"/>
     </row>
-    <row r="862" spans="1:19" ht="11" customHeight="1">
+    <row r="862" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A862" s="8" t="s">
         <v>191</v>
       </c>
@@ -50916,7 +50913,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="863" spans="1:19" ht="11" customHeight="1">
+    <row r="863" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A863" s="8" t="s">
         <v>191</v>
       </c>
@@ -50973,7 +50970,7 @@
       </c>
       <c r="S863" s="10"/>
     </row>
-    <row r="864" spans="1:19" ht="11" customHeight="1">
+    <row r="864" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A864" s="8" t="s">
         <v>191</v>
       </c>
@@ -51030,7 +51027,7 @@
       </c>
       <c r="S864" s="10"/>
     </row>
-    <row r="865" spans="1:19" ht="11" customHeight="1">
+    <row r="865" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A865" s="8" t="s">
         <v>191</v>
       </c>
@@ -51087,7 +51084,7 @@
       </c>
       <c r="S865" s="10"/>
     </row>
-    <row r="866" spans="1:19" ht="11" customHeight="1">
+    <row r="866" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A866" s="8" t="s">
         <v>191</v>
       </c>
@@ -51144,7 +51141,7 @@
       </c>
       <c r="S866" s="10"/>
     </row>
-    <row r="867" spans="1:19" ht="11" customHeight="1">
+    <row r="867" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A867" s="8" t="s">
         <v>191</v>
       </c>
@@ -51201,7 +51198,7 @@
       </c>
       <c r="S867" s="10"/>
     </row>
-    <row r="868" spans="1:19" ht="11" customHeight="1">
+    <row r="868" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A868" s="8" t="s">
         <v>191</v>
       </c>
@@ -51260,7 +51257,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="869" spans="1:19" ht="11" customHeight="1">
+    <row r="869" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A869" s="8" t="s">
         <v>191</v>
       </c>
@@ -51313,7 +51310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="870" spans="1:19" ht="11" customHeight="1">
+    <row r="870" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A870" s="8" t="s">
         <v>191</v>
       </c>
@@ -51370,7 +51367,7 @@
       </c>
       <c r="S870" s="10"/>
     </row>
-    <row r="871" spans="1:19" ht="11" customHeight="1">
+    <row r="871" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A871" s="8" t="s">
         <v>191</v>
       </c>
@@ -51427,7 +51424,7 @@
       </c>
       <c r="S871" s="10"/>
     </row>
-    <row r="872" spans="1:19" ht="11" customHeight="1">
+    <row r="872" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A872" s="8" t="s">
         <v>191</v>
       </c>
@@ -51486,7 +51483,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="873" spans="1:19" ht="11" customHeight="1">
+    <row r="873" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A873" s="8" t="s">
         <v>191</v>
       </c>
@@ -51545,7 +51542,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="874" spans="1:19" ht="11" customHeight="1">
+    <row r="874" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A874" s="8" t="s">
         <v>191</v>
       </c>
@@ -51604,7 +51601,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="875" spans="1:19" ht="11" customHeight="1">
+    <row r="875" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A875" s="8" t="s">
         <v>191</v>
       </c>
@@ -51657,7 +51654,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="876" spans="1:19" ht="11" customHeight="1">
+    <row r="876" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A876" s="8" t="s">
         <v>191</v>
       </c>
@@ -51714,7 +51711,7 @@
       </c>
       <c r="S876" s="10"/>
     </row>
-    <row r="877" spans="1:19" ht="11" customHeight="1">
+    <row r="877" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A877" s="8" t="s">
         <v>191</v>
       </c>
@@ -51773,7 +51770,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="878" spans="1:19" ht="11" customHeight="1">
+    <row r="878" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A878" s="8" t="s">
         <v>191</v>
       </c>
@@ -51832,7 +51829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="879" spans="1:19" ht="11" customHeight="1">
+    <row r="879" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A879" s="8" t="s">
         <v>191</v>
       </c>
@@ -51891,7 +51888,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="880" spans="1:19" ht="11" customHeight="1">
+    <row r="880" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A880" s="8" t="s">
         <v>191</v>
       </c>
@@ -51948,7 +51945,7 @@
       </c>
       <c r="S880" s="10"/>
     </row>
-    <row r="881" spans="1:19" ht="11" customHeight="1">
+    <row r="881" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A881" s="8" t="s">
         <v>191</v>
       </c>
@@ -52005,7 +52002,7 @@
       </c>
       <c r="S881" s="10"/>
     </row>
-    <row r="882" spans="1:19" ht="11" customHeight="1">
+    <row r="882" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A882" s="8" t="s">
         <v>191</v>
       </c>
@@ -52062,7 +52059,7 @@
       </c>
       <c r="S882" s="10"/>
     </row>
-    <row r="883" spans="1:19" ht="11" customHeight="1">
+    <row r="883" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A883" s="8" t="s">
         <v>191</v>
       </c>
@@ -52121,7 +52118,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="884" spans="1:19" ht="11" customHeight="1">
+    <row r="884" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A884" s="8" t="s">
         <v>191</v>
       </c>
@@ -52180,7 +52177,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="885" spans="1:19" ht="11" customHeight="1">
+    <row r="885" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A885" s="8" t="s">
         <v>191</v>
       </c>
@@ -52233,7 +52230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="886" spans="1:19" ht="11" customHeight="1">
+    <row r="886" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A886" s="8" t="s">
         <v>191</v>
       </c>
@@ -52286,7 +52283,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="887" spans="1:19" ht="11" customHeight="1">
+    <row r="887" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A887" s="8" t="s">
         <v>191</v>
       </c>
@@ -52346,6 +52343,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C887" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1112"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S887">
     <sortCondition ref="A2:A887"/>
     <sortCondition ref="B2:B887"/>
